--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MedalList" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
     <t>名称</t>
   </si>
   <si>
-    <t>赌场ID</t>
+    <t>场景ID</t>
   </si>
   <si>
     <t>勋章图标资源</t>
@@ -85,7 +85,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>CasinoId</t>
+    <t>RegionID</t>
   </si>
   <si>
     <t>PicRes</t>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="MedalList" sheetId="1" r:id="rId1"/>
@@ -97,12 +97,35 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+true: 在界面中能看到。
+flase：在界面中不能看到</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 读取前端道具表中的资源
 ..\Assets\AssetsPackage\Common\GameArtsCommon\Common\alats\items</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -147,6 +170,9 @@
     <t>勋章品质</t>
   </si>
   <si>
+    <t>是否开启</t>
+  </si>
+  <si>
     <t>勋章图标</t>
   </si>
   <si>
@@ -154,6 +180,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>bool</t>
   </si>
   <si>
     <t>string</t>
@@ -169,6 +198,9 @@
   </si>
   <si>
     <t>MedalType</t>
+  </si>
+  <si>
+    <t>IsOpen</t>
   </si>
   <si>
     <t>MedalIcon</t>
@@ -214,6 +246,9 @@
   </si>
   <si>
     <t>能量收益：收集达人</t>
+  </si>
+  <si>
+    <t>FLASE</t>
   </si>
   <si>
     <t>daoju1_5.png</t>
@@ -419,12 +454,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -886,7 +921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -910,12 +945,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1442,25 +1471,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:O158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.725" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.725" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.025" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.675" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.2666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="20.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="1" customWidth="1"/>
-    <col min="13" max="13" width="32" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="11.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.675" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.2666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="20.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" customWidth="1"/>
+    <col min="14" max="14" width="32" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:14">
+    <row r="1" customHeight="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1482,71 +1511,80 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:14">
+      <c r="M1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="4"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:14">
+      <c r="M2" s="4"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="I3" s="3"/>
-      <c r="J3" s="4"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:14">
+      <c r="M3" s="4"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:15">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1554,315 +1592,346 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="4"/>
+      <c r="J4" s="3"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:14">
-      <c r="A5" s="8">
+      <c r="M4" s="4"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:15">
+      <c r="A5" s="3">
         <v>1001</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3">
         <v>1200001</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="3">
         <v>1200001</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="F5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3">
         <v>2200001</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="3"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:14">
-      <c r="A6" s="8">
+      <c r="M5" s="4"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:15">
+      <c r="A6" s="3">
         <v>1002</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3">
         <v>1200002</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="3">
         <v>1200002</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="F6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="3">
         <v>2200002</v>
       </c>
-      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="4"/>
+      <c r="J6" s="3"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:14">
-      <c r="A7" s="8">
+      <c r="M6" s="4"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:15">
+      <c r="A7" s="3">
         <v>1003</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3">
         <v>1200003</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="3">
         <v>1200003</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3">
         <v>2200003</v>
       </c>
-      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:14">
-      <c r="A8" s="8">
+      <c r="M7" s="4"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:15">
+      <c r="A8" s="3">
         <v>1004</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3">
         <v>1200004</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="3">
         <v>1200004</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="3">
         <v>2200004</v>
       </c>
-      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:14">
-      <c r="A9" s="8">
+      <c r="M8" s="4"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="6"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:15">
+      <c r="A9" s="3">
         <v>2001</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3">
         <v>1200005</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="3">
         <v>1200005</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="3">
         <v>2200005</v>
       </c>
-      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="4"/>
+      <c r="J9" s="3"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:14">
-      <c r="A10" s="8">
+      <c r="M9" s="4"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="6"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:15">
+      <c r="A10" s="3">
         <v>2002</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="8">
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="3">
         <v>1200006</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="3">
         <v>1200006</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="F10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="3">
         <v>2200006</v>
       </c>
-      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="4"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:14">
-      <c r="A11" s="8">
+      <c r="M10" s="4"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:15">
+      <c r="A11" s="3">
         <v>3001</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3">
         <v>1200007</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="3">
         <v>1200007</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="3">
         <v>3</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="3">
         <v>2200007</v>
       </c>
-      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="4"/>
+      <c r="J11" s="3"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:14">
-      <c r="A12" s="8">
+      <c r="M11" s="4"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:15">
+      <c r="A12" s="3">
         <v>3002</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3">
         <v>1200008</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="3">
         <v>1200008</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="3">
         <v>3</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="3">
         <v>2200008</v>
       </c>
-      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:14">
-      <c r="A13" s="8">
+      <c r="M12" s="4"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:15">
+      <c r="A13" s="3">
         <v>4001</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1200009</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1200009</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8">
-        <v>1200009</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1200009</v>
-      </c>
-      <c r="E13" s="8">
-        <v>4</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="G13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="3">
         <v>2200009</v>
       </c>
-      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:14">
-      <c r="A14" s="8">
+      <c r="M13" s="4"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="3">
         <v>4002</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3">
         <v>1200010</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="3">
         <v>1200010</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="3">
         <v>4</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="3">
         <v>2200010</v>
       </c>
-      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="3"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:14">
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1871,13 +1940,14 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="4"/>
+      <c r="I15" s="3"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:14">
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:15">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1886,13 +1956,14 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:13">
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1901,13 +1972,14 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
+      <c r="I17" s="3"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:13">
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:14">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1916,13 +1988,14 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="4"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:13">
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1931,13 +2004,14 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="4"/>
+      <c r="I19" s="3"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:13">
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:14">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1946,13 +2020,14 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="3"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:13">
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:14">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1961,13 +2036,14 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
+      <c r="I21" s="3"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:13">
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:14">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1976,13 +2052,14 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="3"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:13">
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1991,13 +2068,14 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="3"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:13">
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:14">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2006,13 +2084,14 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:13">
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2021,13 +2100,14 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:13">
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2036,13 +2116,14 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
+      <c r="I26" s="3"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:13">
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2051,13 +2132,14 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="4"/>
+      <c r="I27" s="3"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="6"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:13">
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2066,13 +2148,14 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="3"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:13">
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2081,13 +2164,14 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="3"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:13">
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2096,13 +2180,14 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="3"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:13">
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:14">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2111,13 +2196,14 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="4"/>
+      <c r="I31" s="3"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:13">
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2126,13 +2212,14 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="3"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:13">
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:14">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2141,13 +2228,14 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="3"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:13">
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:14">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2156,13 +2244,14 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:13">
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:14">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2171,13 +2260,14 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="3"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:13">
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2186,13 +2276,14 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="3"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:13">
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2201,13 +2292,14 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="4"/>
+      <c r="I37" s="3"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:13">
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2216,13 +2308,14 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="6"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:13">
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2231,13 +2324,14 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="4"/>
+      <c r="I39" s="3"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="6"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:13">
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:14">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2246,13 +2340,14 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="3"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:13">
+      <c r="L40" s="4"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:14">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2261,13 +2356,14 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="4"/>
+      <c r="I41" s="3"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:13">
+      <c r="L41" s="4"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:14">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2276,13 +2372,14 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="3"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:13">
+      <c r="L42" s="4"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:14">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2291,13 +2388,14 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="3"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:13">
+      <c r="L43" s="4"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:14">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2306,13 +2404,14 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="3"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:13">
+      <c r="L44" s="4"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:14">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2321,13 +2420,14 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="4"/>
+      <c r="I45" s="3"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="6"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:13">
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:14">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2336,13 +2436,14 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="4"/>
+      <c r="I46" s="3"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:13">
+      <c r="L46" s="4"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:14">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2351,13 +2452,14 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="4"/>
+      <c r="I47" s="3"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:13">
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:14">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2366,13 +2468,14 @@
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="4"/>
+      <c r="I48" s="3"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:13">
+      <c r="L48" s="4"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:14">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2381,13 +2484,14 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="4"/>
+      <c r="I49" s="3"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:13">
+      <c r="L49" s="4"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:14">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2396,13 +2500,14 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="4"/>
+      <c r="I50" s="3"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="6"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:13">
+      <c r="L50" s="4"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:14">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2411,13 +2516,14 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="4"/>
+      <c r="I51" s="3"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:13">
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:14">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2426,13 +2532,14 @@
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="4"/>
+      <c r="I52" s="3"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:13">
+      <c r="L52" s="4"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:14">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2441,13 +2548,14 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="4"/>
+      <c r="I53" s="3"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:13">
+      <c r="L53" s="4"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:14">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2456,13 +2564,14 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="4"/>
+      <c r="I54" s="3"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:13">
+      <c r="L54" s="4"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:14">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2471,13 +2580,14 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="4"/>
+      <c r="I55" s="3"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="6"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:13">
+      <c r="L55" s="4"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:14">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2486,13 +2596,14 @@
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="4"/>
+      <c r="I56" s="3"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="6"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:13">
+      <c r="L56" s="4"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:14">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2501,13 +2612,14 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="4"/>
+      <c r="I57" s="3"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:13">
+      <c r="L57" s="4"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:14">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2516,13 +2628,14 @@
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
-      <c r="I58" s="4"/>
+      <c r="I58" s="3"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:13">
+      <c r="L58" s="4"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:14">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2531,13 +2644,14 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="4"/>
+      <c r="I59" s="3"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:13">
+      <c r="L59" s="4"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:14">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2546,13 +2660,14 @@
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="4"/>
+      <c r="I60" s="3"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="6"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:13">
+      <c r="L60" s="4"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:14">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2561,13 +2676,14 @@
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="4"/>
+      <c r="I61" s="3"/>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="6"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:13">
+      <c r="L61" s="4"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:14">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2576,13 +2692,14 @@
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
-      <c r="I62" s="4"/>
+      <c r="I62" s="3"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:13">
+      <c r="L62" s="4"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:14">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2591,13 +2708,14 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="4"/>
+      <c r="I63" s="3"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:13">
+      <c r="L63" s="4"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:14">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2606,13 +2724,14 @@
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="4"/>
+      <c r="I64" s="3"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:13">
+      <c r="L64" s="4"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:14">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2621,13 +2740,14 @@
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="4"/>
+      <c r="I65" s="3"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:13">
+      <c r="L65" s="4"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:14">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2636,13 +2756,14 @@
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
-      <c r="I66" s="4"/>
+      <c r="I66" s="3"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:13">
+      <c r="L66" s="4"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:14">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2651,13 +2772,14 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="4"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:13">
+      <c r="L67" s="4"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:14">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2666,13 +2788,14 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="4"/>
+      <c r="I68" s="3"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:13">
+      <c r="L68" s="4"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:14">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2681,13 +2804,14 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="4"/>
+      <c r="I69" s="3"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:13">
+      <c r="L69" s="4"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:14">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2696,13 +2820,14 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="4"/>
+      <c r="I70" s="3"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:13">
+      <c r="L70" s="4"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:14">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2711,13 +2836,14 @@
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
-      <c r="I71" s="4"/>
+      <c r="I71" s="3"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:13">
+      <c r="L71" s="4"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:14">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2726,13 +2852,14 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="4"/>
+      <c r="I72" s="3"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="6"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:13">
+      <c r="L72" s="4"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:14">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2741,13 +2868,14 @@
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
-      <c r="I73" s="4"/>
+      <c r="I73" s="3"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:13">
+      <c r="L73" s="4"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:14">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2756,13 +2884,14 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="4"/>
+      <c r="I74" s="3"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:13">
+      <c r="L74" s="4"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:14">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2771,13 +2900,14 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
-      <c r="I75" s="4"/>
+      <c r="I75" s="3"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:13">
+      <c r="L75" s="4"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:14">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2786,13 +2916,14 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="4"/>
+      <c r="I76" s="3"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:13">
+      <c r="L76" s="4"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:14">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2801,13 +2932,14 @@
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
-      <c r="I77" s="4"/>
+      <c r="I77" s="3"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:13">
+      <c r="L77" s="4"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:14">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2816,13 +2948,14 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="4"/>
+      <c r="I78" s="3"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:13">
+      <c r="L78" s="4"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:14">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2831,13 +2964,14 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
-      <c r="I79" s="4"/>
+      <c r="I79" s="3"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:13">
+      <c r="L79" s="4"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:14">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2846,13 +2980,14 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
-      <c r="I80" s="4"/>
+      <c r="I80" s="3"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:13">
+      <c r="L80" s="4"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:14">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2861,13 +2996,14 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="I81" s="4"/>
+      <c r="I81" s="3"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:13">
+      <c r="L81" s="4"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:14">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2876,13 +3012,14 @@
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="4"/>
+      <c r="I82" s="3"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
-      <c r="L82" s="5"/>
-      <c r="M82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:13">
+      <c r="L82" s="4"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:14">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2891,13 +3028,14 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
-      <c r="I83" s="4"/>
+      <c r="I83" s="3"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
-      <c r="L83" s="5"/>
-      <c r="M83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:13">
+      <c r="L83" s="4"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:14">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2906,13 +3044,14 @@
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
-      <c r="I84" s="4"/>
+      <c r="I84" s="3"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
-      <c r="L84" s="5"/>
-      <c r="M84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:13">
+      <c r="L84" s="4"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:14">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2921,13 +3060,14 @@
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="4"/>
+      <c r="I85" s="3"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
-      <c r="L85" s="5"/>
-      <c r="M85" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:13">
+      <c r="L85" s="4"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:14">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2936,13 +3076,14 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
-      <c r="I86" s="4"/>
+      <c r="I86" s="3"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
-      <c r="L86" s="5"/>
-      <c r="M86" s="6"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:13">
+      <c r="L86" s="4"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:14">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -2951,13 +3092,14 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-      <c r="I87" s="4"/>
+      <c r="I87" s="3"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
-      <c r="L87" s="5"/>
-      <c r="M87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:13">
+      <c r="L87" s="4"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:14">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -2966,13 +3108,14 @@
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="4"/>
+      <c r="I88" s="3"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
-      <c r="L88" s="5"/>
-      <c r="M88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:13">
+      <c r="L88" s="4"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:14">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -2981,13 +3124,14 @@
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="I89" s="4"/>
+      <c r="I89" s="3"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
-      <c r="L89" s="5"/>
-      <c r="M89" s="6"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:13">
+      <c r="L89" s="4"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:14">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2996,13 +3140,14 @@
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
-      <c r="I90" s="4"/>
+      <c r="I90" s="3"/>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="6"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:13">
+      <c r="L90" s="4"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:14">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3011,13 +3156,14 @@
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
-      <c r="I91" s="4"/>
+      <c r="I91" s="3"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:13">
+      <c r="L91" s="4"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:14">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3026,13 +3172,14 @@
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
-      <c r="I92" s="4"/>
+      <c r="I92" s="3"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:13">
+      <c r="L92" s="4"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:14">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3041,13 +3188,14 @@
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
-      <c r="I93" s="4"/>
+      <c r="I93" s="3"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:13">
+      <c r="L93" s="4"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:14">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3056,13 +3204,14 @@
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
-      <c r="I94" s="4"/>
+      <c r="I94" s="3"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
-      <c r="L94" s="5"/>
-      <c r="M94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:13">
+      <c r="L94" s="4"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:14">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3071,13 +3220,14 @@
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
-      <c r="I95" s="4"/>
+      <c r="I95" s="3"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
-      <c r="L95" s="5"/>
-      <c r="M95" s="6"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:13">
+      <c r="L95" s="4"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:14">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3086,13 +3236,14 @@
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
-      <c r="I96" s="4"/>
+      <c r="I96" s="3"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
-      <c r="L96" s="5"/>
-      <c r="M96" s="6"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:13">
+      <c r="L96" s="4"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:14">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3101,13 +3252,14 @@
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="4"/>
+      <c r="I97" s="3"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="6"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:13">
+      <c r="L97" s="4"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:14">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3116,13 +3268,14 @@
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="4"/>
+      <c r="I98" s="3"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:13">
+      <c r="L98" s="4"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:14">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3131,13 +3284,14 @@
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
-      <c r="I99" s="4"/>
+      <c r="I99" s="3"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:13">
+      <c r="L99" s="4"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:14">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3146,13 +3300,14 @@
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
-      <c r="I100" s="4"/>
+      <c r="I100" s="3"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:13">
+      <c r="L100" s="4"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:14">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3161,13 +3316,14 @@
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
-      <c r="I101" s="4"/>
+      <c r="I101" s="3"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
-      <c r="L101" s="5"/>
-      <c r="M101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:13">
+      <c r="L101" s="4"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:14">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -3176,13 +3332,14 @@
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
-      <c r="I102" s="4"/>
+      <c r="I102" s="3"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
-      <c r="L102" s="5"/>
-      <c r="M102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:13">
+      <c r="L102" s="4"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:14">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -3191,13 +3348,14 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
-      <c r="I103" s="4"/>
+      <c r="I103" s="3"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
-      <c r="L103" s="5"/>
-      <c r="M103" s="6"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:13">
+      <c r="L103" s="4"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:14">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -3206,13 +3364,14 @@
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
-      <c r="I104" s="4"/>
+      <c r="I104" s="3"/>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="6"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:13">
+      <c r="L104" s="4"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:14">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -3221,13 +3380,14 @@
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
-      <c r="I105" s="4"/>
+      <c r="I105" s="3"/>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
-      <c r="L105" s="5"/>
-      <c r="M105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:13">
+      <c r="L105" s="4"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:14">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3236,13 +3396,14 @@
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
-      <c r="I106" s="4"/>
+      <c r="I106" s="3"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:13">
+      <c r="L106" s="4"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:14">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -3251,13 +3412,14 @@
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
-      <c r="I107" s="4"/>
+      <c r="I107" s="3"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
-      <c r="L107" s="5"/>
-      <c r="M107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:13">
+      <c r="L107" s="4"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:14">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -3266,13 +3428,14 @@
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
-      <c r="I108" s="4"/>
+      <c r="I108" s="3"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
-      <c r="L108" s="5"/>
-      <c r="M108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:13">
+      <c r="L108" s="4"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:14">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3281,13 +3444,14 @@
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
-      <c r="I109" s="4"/>
+      <c r="I109" s="3"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
-      <c r="L109" s="5"/>
-      <c r="M109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:13">
+      <c r="L109" s="4"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:14">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3296,13 +3460,14 @@
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
-      <c r="I110" s="4"/>
+      <c r="I110" s="3"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
-      <c r="L110" s="5"/>
-      <c r="M110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:13">
+      <c r="L110" s="4"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:14">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -3311,13 +3476,14 @@
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
-      <c r="I111" s="4"/>
+      <c r="I111" s="3"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:13">
+      <c r="L111" s="4"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:14">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -3326,13 +3492,14 @@
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
-      <c r="I112" s="4"/>
+      <c r="I112" s="3"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
-      <c r="L112" s="5"/>
-      <c r="M112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:13">
+      <c r="L112" s="4"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:14">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -3341,13 +3508,14 @@
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
-      <c r="I113" s="4"/>
+      <c r="I113" s="3"/>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
-      <c r="L113" s="5"/>
-      <c r="M113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:13">
+      <c r="L113" s="4"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:14">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -3356,13 +3524,14 @@
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
-      <c r="I114" s="4"/>
+      <c r="I114" s="3"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
-      <c r="L114" s="5"/>
-      <c r="M114" s="6"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:13">
+      <c r="L114" s="4"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:14">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -3371,13 +3540,14 @@
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
-      <c r="I115" s="4"/>
+      <c r="I115" s="3"/>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
-      <c r="L115" s="5"/>
-      <c r="M115" s="6"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:13">
+      <c r="L115" s="4"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:14">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -3386,13 +3556,14 @@
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
-      <c r="I116" s="4"/>
+      <c r="I116" s="3"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
-      <c r="L116" s="5"/>
-      <c r="M116" s="6"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:13">
+      <c r="L116" s="4"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:14">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -3401,13 +3572,14 @@
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
-      <c r="I117" s="4"/>
+      <c r="I117" s="3"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
-      <c r="L117" s="5"/>
-      <c r="M117" s="6"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:13">
+      <c r="L117" s="4"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:14">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3416,501 +3588,542 @@
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
-      <c r="I118" s="4"/>
+      <c r="I118" s="3"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
-      <c r="L118" s="5"/>
-      <c r="M118" s="6"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:13">
+      <c r="L118" s="4"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:14">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="4"/>
-      <c r="L119" s="5"/>
-      <c r="M119" s="6"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:13">
+      <c r="G119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="4"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:14">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="4"/>
-      <c r="L120" s="5"/>
-      <c r="M120" s="6"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:13">
+      <c r="G120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="4"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:14">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="4"/>
-      <c r="L121" s="5"/>
-      <c r="M121" s="6"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:13">
+      <c r="G121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="4"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:14">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="4"/>
-      <c r="L122" s="5"/>
-      <c r="M122" s="6"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:13">
+      <c r="G122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="4"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:14">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="4"/>
-      <c r="L123" s="5"/>
-      <c r="M123" s="6"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:13">
+      <c r="G123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="4"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:14">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-      <c r="H124" s="3"/>
-      <c r="I124" s="4"/>
-      <c r="L124" s="5"/>
-      <c r="M124" s="6"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:13">
+      <c r="G124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="4"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:14">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
-      <c r="H125" s="3"/>
-      <c r="I125" s="4"/>
-      <c r="L125" s="5"/>
-      <c r="M125" s="6"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:13">
+      <c r="G125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="4"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:14">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="4"/>
-      <c r="L126" s="5"/>
-      <c r="M126" s="6"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:13">
+      <c r="G126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="4"/>
+      <c r="M126" s="5"/>
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:14">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-      <c r="H127" s="3"/>
-      <c r="I127" s="4"/>
-      <c r="L127" s="5"/>
-      <c r="M127" s="6"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:13">
+      <c r="G127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="4"/>
+      <c r="M127" s="5"/>
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:14">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="4"/>
-      <c r="L128" s="5"/>
-      <c r="M128" s="6"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:13">
+      <c r="G128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="4"/>
+      <c r="M128" s="5"/>
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:14">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="4"/>
-      <c r="K129" s="4"/>
-      <c r="L129" s="5"/>
-      <c r="M129" s="6"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:13">
+      <c r="G129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="5"/>
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:14">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="4"/>
-      <c r="K130" s="4"/>
-      <c r="L130" s="5"/>
-      <c r="M130" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:13">
+      <c r="G130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="4"/>
+      <c r="L130" s="4"/>
+      <c r="M130" s="5"/>
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:14">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="4"/>
-      <c r="K131" s="4"/>
-      <c r="L131" s="5"/>
-      <c r="M131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:13">
+      <c r="G131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="4"/>
+      <c r="L131" s="4"/>
+      <c r="M131" s="5"/>
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:14">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="4"/>
-      <c r="K132" s="4"/>
-      <c r="L132" s="5"/>
-      <c r="M132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:13">
+      <c r="G132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="4"/>
+      <c r="L132" s="4"/>
+      <c r="M132" s="5"/>
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:14">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="4"/>
-      <c r="K133" s="4"/>
-      <c r="L133" s="5"/>
-      <c r="M133" s="6"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:13">
+      <c r="G133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="4"/>
+      <c r="L133" s="4"/>
+      <c r="M133" s="5"/>
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:14">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
-      <c r="H134" s="3"/>
-      <c r="I134" s="4"/>
-      <c r="K134" s="4"/>
-      <c r="L134" s="5"/>
-      <c r="M134" s="6"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:13">
+      <c r="G134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="4"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="5"/>
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:14">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="4"/>
-      <c r="K135" s="4"/>
-      <c r="L135" s="5"/>
-      <c r="M135" s="6"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:13">
+      <c r="G135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="4"/>
+      <c r="L135" s="4"/>
+      <c r="M135" s="5"/>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:14">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-      <c r="H136" s="3"/>
-      <c r="I136" s="4"/>
-      <c r="K136" s="4"/>
-      <c r="L136" s="5"/>
-      <c r="M136" s="6"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:13">
+      <c r="G136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="4"/>
+      <c r="L136" s="4"/>
+      <c r="M136" s="5"/>
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:14">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
-      <c r="H137" s="3"/>
-      <c r="I137" s="4"/>
-      <c r="K137" s="4"/>
-      <c r="L137" s="5"/>
-      <c r="M137" s="6"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:13">
+      <c r="G137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="4"/>
+      <c r="L137" s="4"/>
+      <c r="M137" s="5"/>
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:14">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
-      <c r="H138" s="3"/>
-      <c r="I138" s="4"/>
-      <c r="K138" s="4"/>
-      <c r="L138" s="5"/>
-      <c r="M138" s="6"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:13">
+      <c r="G138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="4"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="5"/>
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:14">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="4"/>
-      <c r="L139" s="5"/>
-      <c r="M139" s="6"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:13">
+      <c r="G139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="4"/>
+      <c r="M139" s="5"/>
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:14">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="4"/>
-      <c r="L140" s="5"/>
-      <c r="M140" s="6"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:13">
+      <c r="G140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="4"/>
+      <c r="M140" s="5"/>
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:14">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="4"/>
-      <c r="L141" s="5"/>
-      <c r="M141" s="6"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:13">
+      <c r="G141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="4"/>
+      <c r="M141" s="5"/>
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:14">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="4"/>
-      <c r="L142" s="5"/>
-      <c r="M142" s="6"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:13">
+      <c r="G142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="4"/>
+      <c r="M142" s="5"/>
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:14">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-      <c r="H143" s="3"/>
-      <c r="I143" s="4"/>
-      <c r="L143" s="5"/>
-      <c r="M143" s="6"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:13">
+      <c r="G143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="4"/>
+      <c r="M143" s="5"/>
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:14">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-      <c r="H144" s="3"/>
-      <c r="I144" s="4"/>
-      <c r="L144" s="5"/>
-      <c r="M144" s="6"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:13">
+      <c r="G144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="4"/>
+      <c r="M144" s="5"/>
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:14">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
-      <c r="H145" s="3"/>
-      <c r="I145" s="4"/>
-      <c r="L145" s="5"/>
-      <c r="M145" s="6"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:13">
+      <c r="G145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="4"/>
+      <c r="M145" s="5"/>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:14">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
-      <c r="H146" s="3"/>
-      <c r="I146" s="4"/>
-      <c r="L146" s="5"/>
-      <c r="M146" s="6"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:13">
+      <c r="G146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="4"/>
+      <c r="M146" s="5"/>
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:14">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="I147" s="4"/>
-      <c r="L147" s="5"/>
-      <c r="M147" s="6"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:13">
+      <c r="G147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="4"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:14">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
-      <c r="H148" s="3"/>
-      <c r="I148" s="4"/>
-      <c r="L148" s="5"/>
-      <c r="M148" s="6"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:13">
+      <c r="G148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="4"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:14">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
-      <c r="H149" s="3"/>
-      <c r="I149" s="4"/>
-      <c r="L149" s="5"/>
-      <c r="M149" s="6"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:13">
+      <c r="G149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="4"/>
+      <c r="M149" s="5"/>
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:14">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
-      <c r="H150" s="3"/>
-      <c r="I150" s="4"/>
-      <c r="L150" s="5"/>
-      <c r="M150" s="6"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:13">
+      <c r="G150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="4"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:14">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="4"/>
-      <c r="L151" s="5"/>
-      <c r="M151" s="6"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:13">
+      <c r="G151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="4"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:14">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
-      <c r="H152" s="3"/>
-      <c r="I152" s="4"/>
-      <c r="L152" s="5"/>
-      <c r="M152" s="6"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:13">
+      <c r="G152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="4"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:14">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
-      <c r="H153" s="3"/>
-      <c r="I153" s="4"/>
-      <c r="L153" s="5"/>
-      <c r="M153" s="6"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:13">
+      <c r="G153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="4"/>
+      <c r="M153" s="5"/>
+      <c r="N153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:14">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
-      <c r="H154" s="3"/>
-      <c r="I154" s="4"/>
-      <c r="L154" s="5"/>
-      <c r="M154" s="6"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:13">
+      <c r="G154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="4"/>
+      <c r="M154" s="5"/>
+      <c r="N154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:14">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
-      <c r="H155" s="3"/>
-      <c r="I155" s="4"/>
-      <c r="L155" s="5"/>
-      <c r="M155" s="6"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:13">
+      <c r="G155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="4"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:14">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
-      <c r="H156" s="3"/>
-      <c r="I156" s="4"/>
-      <c r="L156" s="5"/>
-      <c r="M156" s="6"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:13">
+      <c r="G156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="4"/>
+      <c r="M156" s="5"/>
+      <c r="N156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:14">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
-      <c r="H157" s="3"/>
-      <c r="I157" s="4"/>
-      <c r="L157" s="5"/>
-      <c r="M157" s="6"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:13">
+      <c r="G157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="4"/>
+      <c r="M157" s="5"/>
+      <c r="N157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:14">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
-      <c r="H158" s="3"/>
-      <c r="I158" s="4"/>
-      <c r="L158" s="5"/>
-      <c r="M158" s="6"/>
+      <c r="G158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="4"/>
+      <c r="M158" s="5"/>
+      <c r="N158" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
   <si>
     <t>序号</t>
   </si>
@@ -68,6 +68,12 @@
     <t>#名称</t>
   </si>
   <si>
+    <t>#对应任务</t>
+  </si>
+  <si>
+    <t>多语言ID</t>
+  </si>
+  <si>
     <t>需求激活道具ID</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>MedalNameId</t>
+  </si>
+  <si>
     <t>NeedItemId</t>
   </si>
   <si>
@@ -92,90 +101,177 @@
     <t>打卡卫士</t>
   </si>
   <si>
+    <t>累积登陆N天</t>
+  </si>
+  <si>
     <t>成长之路</t>
   </si>
   <si>
+    <t>角色等级达到N级</t>
+  </si>
+  <si>
     <t>转轮高手</t>
   </si>
   <si>
+    <t>SLOT游戏旋转N次</t>
+  </si>
+  <si>
     <t>大赢家</t>
   </si>
   <si>
+    <t>SLOT游戏赢奖N金币</t>
+  </si>
+  <si>
     <t>转轮精英</t>
   </si>
   <si>
+    <t>SLOT游戏获得N个X道具</t>
+  </si>
+  <si>
     <t>幸运之星</t>
   </si>
   <si>
+    <t>累计触发免费游戏模式N次</t>
+  </si>
+  <si>
     <t>游戏收集者</t>
   </si>
   <si>
+    <t>累积研发N个游戏</t>
+  </si>
+  <si>
     <t>建筑能手</t>
   </si>
   <si>
+    <t>建筑累积升级N次</t>
+  </si>
+  <si>
     <t>百万富豪</t>
   </si>
   <si>
+    <t>在经营中 金币收益累积达到N</t>
+  </si>
+  <si>
     <t>能量收集者</t>
   </si>
   <si>
+    <t>在经营中 能量收益累积达到N</t>
+  </si>
+  <si>
     <t>金币大师</t>
   </si>
   <si>
+    <t>累积消费N金币</t>
+  </si>
+  <si>
     <t>钻石富豪</t>
   </si>
   <si>
+    <t>累积消费N钻石</t>
+  </si>
+  <si>
     <t>招商能手</t>
   </si>
   <si>
+    <t>招商N次游客</t>
+  </si>
+  <si>
     <t>娱乐CEO</t>
   </si>
   <si>
+    <t>观看N次广告</t>
+  </si>
+  <si>
     <t>人气爆棚</t>
   </si>
   <si>
+    <t>累积拜访N次</t>
+  </si>
+  <si>
     <t>建筑大师</t>
   </si>
   <si>
+    <t>拥有N个X级以上的建筑</t>
+  </si>
+  <si>
     <t>人气之王</t>
   </si>
   <si>
+    <t>拥有N个X星以上的游客</t>
+  </si>
+  <si>
     <t>团队高管</t>
   </si>
   <si>
+    <t>拥有N个X星以上的雇员</t>
+  </si>
+  <si>
     <t>培养能手</t>
   </si>
   <si>
+    <t>拥有N个X星娱乐类型的雇员</t>
+  </si>
+  <si>
     <t>培养大师</t>
   </si>
   <si>
+    <t>拥有N个X星休闲类型的雇员</t>
+  </si>
+  <si>
     <t>培养专家</t>
   </si>
   <si>
+    <t>拥有N个X星管理类型的雇员</t>
+  </si>
+  <si>
     <t>有点小钱</t>
   </si>
   <si>
+    <t>累积触发 MEGA WIN N次</t>
+  </si>
+  <si>
     <t>小有成就</t>
   </si>
   <si>
+    <t>累积触发 LEGENDARY WIN  N次</t>
+  </si>
+  <si>
     <t>中奖能手</t>
   </si>
   <si>
+    <t>累积触发 EPIC WIN  N次</t>
+  </si>
+  <si>
     <t>招财进宝</t>
   </si>
   <si>
+    <t>累积触发 MINOR奖池 N次</t>
+  </si>
+  <si>
     <t>财富自由</t>
   </si>
   <si>
+    <t>累积触发 MAJOR奖池  N次</t>
+  </si>
+  <si>
     <t>超级赢家</t>
   </si>
   <si>
+    <t>累积触发 GRAND奖池  N次</t>
+  </si>
+  <si>
     <t>VIP专享</t>
   </si>
   <si>
+    <t>角色VIP等级达到N级</t>
+  </si>
+  <si>
     <t>研发院士</t>
   </si>
   <si>
+    <t>研究院的研发能力达到X</t>
+  </si>
+  <si>
     <t>社交精英</t>
   </si>
   <si>
@@ -213,6 +309,9 @@
   </si>
   <si>
     <t>财富神话</t>
+  </si>
+  <si>
+    <t>累积充值达到N美元</t>
   </si>
   <si>
     <t>财运亨通</t>
@@ -285,7 +384,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +408,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -794,137 +899,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -947,6 +1052,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1474,22 +1582,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.725" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.725" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="20.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24" style="1" customWidth="1"/>
-    <col min="10" max="10" width="32" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="28.375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.175" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="20.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24" style="1" customWidth="1"/>
+    <col min="12" max="12" width="32" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1502,2340 +1611,2846 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="3">
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:13">
+      <c r="A5" s="8">
         <v>1001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3">
         <v>1150001</v>
       </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="E5" s="3">
+        <v>1150001</v>
+      </c>
+      <c r="F5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:13">
       <c r="A6" s="3">
         <v>1002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
         <v>1150002</v>
       </c>
-      <c r="D6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="E6" s="3">
+        <v>1150002</v>
+      </c>
+      <c r="F6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="3">
         <v>1003</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3">
         <v>1150003</v>
       </c>
-      <c r="D7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="E7" s="3">
+        <v>1150003</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
       <c r="A8" s="3">
         <v>1004</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3">
         <v>1150004</v>
       </c>
-      <c r="D8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="E8" s="3">
+        <v>1150004</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
       <c r="A9" s="3">
         <v>1005</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3">
         <v>1150005</v>
       </c>
-      <c r="D9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="E9" s="3">
+        <v>1150005</v>
+      </c>
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
       <c r="A10" s="3">
         <v>1006</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3">
         <v>1150006</v>
       </c>
-      <c r="D10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="E10" s="3">
+        <v>1150006</v>
+      </c>
+      <c r="F10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
       <c r="A11" s="3">
         <v>1007</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
         <v>1150007</v>
       </c>
-      <c r="D11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="E11" s="3">
+        <v>1150007</v>
+      </c>
+      <c r="F11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
       <c r="A12" s="3">
         <v>1008</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3">
         <v>1150008</v>
       </c>
-      <c r="D12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="E12" s="3">
+        <v>1150008</v>
+      </c>
+      <c r="F12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
       <c r="A13" s="3">
         <v>1009</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3">
+        <v>28</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="3">
         <v>1150009</v>
       </c>
-      <c r="D13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="E13" s="3">
+        <v>1150009</v>
+      </c>
+      <c r="F13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
       <c r="A14" s="3">
         <v>1010</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="3">
         <v>1150010</v>
       </c>
-      <c r="D14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="E14" s="3">
+        <v>1150010</v>
+      </c>
+      <c r="F14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
       <c r="A15" s="3">
         <v>1011</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3">
         <v>1150011</v>
       </c>
-      <c r="D15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="E15" s="3">
+        <v>1150011</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
       <c r="A16" s="3">
         <v>1012</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3">
         <v>1150012</v>
       </c>
-      <c r="D16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="E16" s="3">
+        <v>1150012</v>
+      </c>
+      <c r="F16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:10">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
       <c r="A17" s="3">
         <v>1013</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="3">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="3">
         <v>1150013</v>
       </c>
-      <c r="D17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="E17" s="3">
+        <v>1150013</v>
+      </c>
+      <c r="F17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:10">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
       <c r="A18" s="3">
         <v>1014</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="3">
         <v>1150014</v>
       </c>
-      <c r="D18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="E18" s="3">
+        <v>1150014</v>
+      </c>
+      <c r="F18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:10">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
       <c r="A19" s="3">
         <v>1015</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="3">
         <v>1150015</v>
       </c>
-      <c r="D19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="3">
+        <v>1150015</v>
+      </c>
+      <c r="F19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:10">
-      <c r="A20" s="3">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
+      <c r="A20" s="8">
         <v>2001</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="3">
         <v>1150016</v>
       </c>
-      <c r="D20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="E20" s="3">
+        <v>1150016</v>
+      </c>
+      <c r="F20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:10">
-      <c r="A21" s="3">
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
+      <c r="A21" s="8">
         <v>2002</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="3">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="3">
         <v>1150017</v>
       </c>
-      <c r="D21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="E21" s="3">
+        <v>1150017</v>
+      </c>
+      <c r="F21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:10">
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
       <c r="A22" s="3">
         <v>2003</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="3">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="3">
         <v>1150018</v>
       </c>
-      <c r="D22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="E22" s="3">
+        <v>1150018</v>
+      </c>
+      <c r="F22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:10">
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
       <c r="A23" s="3">
         <v>2004</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3">
+        <v>48</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="3">
         <v>1150019</v>
       </c>
-      <c r="D23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="E23" s="3">
+        <v>1150019</v>
+      </c>
+      <c r="F23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:10">
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24" s="3">
         <v>2005</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="3">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="3">
         <v>1150020</v>
       </c>
-      <c r="D24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="E24" s="3">
+        <v>1150020</v>
+      </c>
+      <c r="F24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:10">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25" s="3">
         <v>2006</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="3">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3">
         <v>1150021</v>
       </c>
-      <c r="D25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="E25" s="3">
+        <v>1150021</v>
+      </c>
+      <c r="F25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:10">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26" s="3">
         <v>2007</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="3">
+        <v>54</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3">
         <v>1150022</v>
       </c>
-      <c r="D26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="E26" s="3">
+        <v>1150022</v>
+      </c>
+      <c r="F26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:10">
-      <c r="A27" s="3">
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
+      <c r="A27" s="8">
         <v>2008</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="3">
+        <v>56</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="3">
         <v>1150023</v>
       </c>
-      <c r="D27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="E27" s="3">
+        <v>1150023</v>
+      </c>
+      <c r="F27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:10">
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28" s="3">
         <v>2009</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="3">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="3">
         <v>1150024</v>
       </c>
-      <c r="D28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="E28" s="3">
+        <v>1150024</v>
+      </c>
+      <c r="F28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:10">
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29" s="3">
         <v>2010</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="3">
+        <v>60</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="3">
         <v>1150025</v>
       </c>
-      <c r="D29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="E29" s="3">
+        <v>1150025</v>
+      </c>
+      <c r="F29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:10">
-      <c r="A30" s="3">
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="A30" s="8">
         <v>2011</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="3">
+        <v>62</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="3">
         <v>1150026</v>
       </c>
-      <c r="D30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="E30" s="3">
+        <v>1150026</v>
+      </c>
+      <c r="F30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:10">
-      <c r="A31" s="3">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="A31" s="8">
         <v>2012</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="3">
+        <v>64</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="3">
         <v>1150027</v>
       </c>
-      <c r="D31" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="E31" s="3">
+        <v>1150027</v>
+      </c>
+      <c r="F31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:10">
-      <c r="A32" s="3">
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
+      <c r="A32" s="8">
         <v>3001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="3">
+        <v>66</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="3">
         <v>1150028</v>
       </c>
-      <c r="D32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="E32" s="3">
+        <v>1150028</v>
+      </c>
+      <c r="F32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:10">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:12">
       <c r="A33" s="3">
         <v>3002</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="3">
+        <v>68</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="3">
         <v>1150029</v>
       </c>
-      <c r="D33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="E33" s="3">
+        <v>1150029</v>
+      </c>
+      <c r="F33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:10">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:12">
       <c r="A34" s="3">
         <v>3003</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="3">
+        <v>70</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3">
         <v>1150030</v>
       </c>
-      <c r="D34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+      <c r="E34" s="3">
+        <v>1150030</v>
+      </c>
+      <c r="F34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:10">
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:12">
       <c r="A35" s="3">
         <v>3004</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="3">
+        <v>71</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3">
         <v>1150031</v>
       </c>
-      <c r="D35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
+      <c r="E35" s="3">
+        <v>1150031</v>
+      </c>
+      <c r="F35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:10">
-      <c r="A36" s="3">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:12">
+      <c r="A36" s="8">
         <v>3005</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="3">
+        <v>72</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3">
         <v>1150032</v>
       </c>
-      <c r="D36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="E36" s="3">
+        <v>1150032</v>
+      </c>
+      <c r="F36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:10">
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
       <c r="A37" s="3">
         <v>3006</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="3">
+        <v>73</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3">
         <v>1150033</v>
       </c>
-      <c r="D37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="E37" s="3">
+        <v>1150033</v>
+      </c>
+      <c r="F37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="4"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:10">
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
       <c r="A38" s="3">
         <v>3007</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="3">
+        <v>74</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3">
         <v>1150034</v>
       </c>
-      <c r="D38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
+      <c r="E38" s="3">
+        <v>1150034</v>
+      </c>
+      <c r="F38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:10">
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
       <c r="A39" s="3">
         <v>3008</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="3">
+        <v>75</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3">
         <v>1150035</v>
       </c>
-      <c r="D39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
+      <c r="E39" s="3">
+        <v>1150035</v>
+      </c>
+      <c r="F39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:10">
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
       <c r="A40" s="3">
         <v>3009</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="3">
+        <v>76</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3">
         <v>1150036</v>
       </c>
-      <c r="D40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
+      <c r="E40" s="3">
+        <v>1150036</v>
+      </c>
+      <c r="F40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:10">
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
       <c r="A41" s="3">
         <v>3010</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="3">
+        <v>77</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3">
         <v>1150037</v>
       </c>
-      <c r="D41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
+      <c r="E41" s="3">
+        <v>1150037</v>
+      </c>
+      <c r="F41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:10">
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
       <c r="A42" s="3">
         <v>3011</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="3">
+        <v>78</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3">
         <v>1150038</v>
       </c>
-      <c r="D42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="E42" s="3">
+        <v>1150038</v>
+      </c>
+      <c r="F42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:10">
-      <c r="A43" s="3">
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
+      <c r="A43" s="8">
         <v>3012</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="3">
+        <v>79</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3">
         <v>1150039</v>
       </c>
-      <c r="D43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
+      <c r="E43" s="3">
+        <v>1150039</v>
+      </c>
+      <c r="F43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:10">
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
       <c r="A44" s="3">
         <v>3013</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="3">
+        <v>80</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <v>1150040</v>
       </c>
-      <c r="D44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
+      <c r="E44" s="3">
+        <v>1150040</v>
+      </c>
+      <c r="F44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:10">
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
       <c r="A45" s="3">
         <v>3014</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="3">
+        <v>81</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3">
         <v>1150041</v>
       </c>
-      <c r="D45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
+      <c r="E45" s="3">
+        <v>1150041</v>
+      </c>
+      <c r="F45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:10">
-      <c r="A46" s="3">
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
+      <c r="A46" s="8">
         <v>4001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="3">
+        <v>82</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="3">
         <v>1150042</v>
       </c>
-      <c r="D46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="E46" s="3">
+        <v>1150042</v>
+      </c>
+      <c r="F46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:10">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
       <c r="A47" s="3">
         <v>4002</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="3">
+        <v>84</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3">
         <v>1150043</v>
       </c>
-      <c r="D47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
+      <c r="E47" s="3">
+        <v>1150043</v>
+      </c>
+      <c r="F47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="4"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:10">
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:12">
       <c r="A48" s="3">
         <v>4003</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="3">
+        <v>85</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3">
         <v>1150044</v>
       </c>
-      <c r="D48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
+      <c r="E48" s="3">
+        <v>1150044</v>
+      </c>
+      <c r="F48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="4"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:10">
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:12">
       <c r="A49" s="3">
         <v>4004</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="3">
+        <v>86</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3">
         <v>1150045</v>
       </c>
-      <c r="D49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="E49" s="3">
+        <v>1150045</v>
+      </c>
+      <c r="F49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="4"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:10">
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:12">
       <c r="A50" s="3">
         <v>4005</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="3">
+        <v>87</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3">
         <v>1150046</v>
       </c>
-      <c r="D50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="E50" s="3">
+        <v>1150046</v>
+      </c>
+      <c r="F50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="4"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:10">
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:12">
       <c r="A51" s="3">
         <v>4006</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="3">
+        <v>88</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3">
         <v>1150047</v>
       </c>
-      <c r="D51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="E51" s="3">
+        <v>1150047</v>
+      </c>
+      <c r="F51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="4"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:10">
-      <c r="A52" s="3">
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:12">
+      <c r="A52" s="8">
         <v>4007</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52" s="3">
+        <v>89</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3">
         <v>1150048</v>
       </c>
-      <c r="D52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="E52" s="3">
+        <v>1150048</v>
+      </c>
+      <c r="F52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:10">
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:12">
       <c r="A53" s="3">
         <v>4008</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="3">
+        <v>90</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3">
         <v>1150049</v>
       </c>
-      <c r="D53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="E53" s="3">
+        <v>1150049</v>
+      </c>
+      <c r="F53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:10">
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:12">
       <c r="A54" s="3">
         <v>4009</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54" s="3">
+        <v>91</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3">
         <v>1150050</v>
       </c>
-      <c r="D54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="E54" s="3">
+        <v>1150050</v>
+      </c>
+      <c r="F54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="4"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:10">
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:12">
       <c r="A55" s="3">
         <v>4010</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C55" s="3">
+        <v>92</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3">
         <v>1150051</v>
       </c>
-      <c r="D55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
+      <c r="E55" s="3">
+        <v>1150051</v>
+      </c>
+      <c r="F55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3"/>
       <c r="H55" s="4"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:10">
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:12">
       <c r="A56" s="3">
         <v>4011</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56" s="3">
+        <v>93</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3">
         <v>1150052</v>
       </c>
-      <c r="D56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
+      <c r="E56" s="3">
+        <v>1150052</v>
+      </c>
+      <c r="F56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="4"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="6"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:10">
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:12">
       <c r="A57" s="3">
         <v>4012</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="3">
+        <v>94</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3">
         <v>1150053</v>
       </c>
-      <c r="D57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+      <c r="E57" s="3">
+        <v>1150053</v>
+      </c>
+      <c r="F57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="4"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:10">
-      <c r="A58" s="3">
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:12">
+      <c r="A58" s="8">
         <v>4013</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" s="3">
+        <v>95</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3">
         <v>1150054</v>
       </c>
-      <c r="D58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+      <c r="E58" s="3">
+        <v>1150054</v>
+      </c>
+      <c r="F58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="4"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:10">
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:12">
       <c r="A59" s="3">
         <v>4014</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" s="3">
+        <v>96</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3">
         <v>1150055</v>
       </c>
-      <c r="D59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
+      <c r="E59" s="3">
+        <v>1150055</v>
+      </c>
+      <c r="F59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="4"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:10">
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:12">
       <c r="A60" s="3">
         <v>4015</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="3">
+        <v>97</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3">
         <v>1150056</v>
       </c>
-      <c r="D60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="E60" s="3">
+        <v>1150056</v>
+      </c>
+      <c r="F60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3"/>
       <c r="H60" s="4"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="6"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:10">
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
       <c r="A61" s="3">
         <v>4016</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" s="3">
+        <v>98</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3">
         <v>1150057</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="E61" s="3">
+        <v>1150057</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" s="3"/>
       <c r="H61" s="4"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="6"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:10">
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
       <c r="A62" s="3">
         <v>4017</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62" s="3">
+        <v>100</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
         <v>1150058</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
+      <c r="E62" s="3">
+        <v>1150058</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="4"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:10">
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
       <c r="A63" s="3">
         <v>4018</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" s="3">
+        <v>101</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3">
         <v>1150059</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
+      <c r="E63" s="3">
+        <v>1150059</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:10">
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
       <c r="A64" s="3">
         <v>4019</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64" s="3">
+        <v>102</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3">
         <v>1150060</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E64" s="3"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
+      <c r="E64" s="3">
+        <v>1150060</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="4"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:10">
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:12">
       <c r="A65" s="3">
         <v>4020</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="3">
+        <v>103</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3">
         <v>1150061</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="E65" s="3">
+        <v>1150061</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="4"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:10">
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:12">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="4"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:10">
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:12">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
       <c r="H67" s="4"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:10">
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:12">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
       <c r="H68" s="4"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:10">
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:12">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="4"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:10">
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:12">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
       <c r="H70" s="4"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:10">
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:12">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
       <c r="H71" s="4"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:10">
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:12">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
       <c r="H72" s="4"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="6"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:10">
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:12">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
       <c r="H73" s="4"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:10">
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:12">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
       <c r="H74" s="4"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:10">
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:12">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:10">
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:12">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:10">
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:12">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:10">
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:12">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:10">
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:12">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:10">
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:12">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:10">
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:12">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:10">
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:12">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
       <c r="H82" s="4"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:10">
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:12">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
       <c r="H83" s="4"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:10">
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:12">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
       <c r="H84" s="4"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:10">
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:12">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
       <c r="H85" s="4"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:10">
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
       <c r="H86" s="4"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="6"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:10">
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
       <c r="H87" s="4"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:10">
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:12">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
       <c r="H88" s="4"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:10">
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:12">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
       <c r="H89" s="4"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="6"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:10">
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:12">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
       <c r="H90" s="4"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="6"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:10">
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
       <c r="H91" s="4"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:10">
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
       <c r="H92" s="4"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:10">
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
       <c r="H93" s="4"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:10">
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:12">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
       <c r="H94" s="4"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:10">
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:12">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
       <c r="H95" s="4"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="6"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:10">
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:12">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
       <c r="H96" s="4"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="6"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:10">
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:12">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
       <c r="H97" s="4"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="6"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:10">
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:12">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
       <c r="H98" s="4"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:10">
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:12">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
       <c r="H99" s="4"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:10">
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
       <c r="H100" s="4"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:10">
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
       <c r="H101" s="4"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:10">
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
       <c r="H102" s="4"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:10">
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
       <c r="H103" s="4"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="6"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:10">
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="6"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:10">
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:10">
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:12">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
       <c r="H106" s="4"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:10">
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:12">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
       <c r="H107" s="4"/>
-      <c r="I107" s="5"/>
-      <c r="J107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:10">
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:12">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
       <c r="H108" s="4"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:10">
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:12">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
       <c r="H109" s="4"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:10">
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:12">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
       <c r="H110" s="4"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:10">
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:12">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
       <c r="H111" s="4"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:10">
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:12">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
       <c r="H112" s="4"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:10">
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:12">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
       <c r="H113" s="4"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:10">
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:12">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
       <c r="H114" s="4"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="6"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:10">
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:12">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
       <c r="H115" s="4"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="6"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:10">
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:12">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
       <c r="H116" s="4"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="6"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:10">
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:12">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
       <c r="H117" s="4"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="6"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:10">
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:12">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
       <c r="H118" s="4"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="6"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:10">
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="5"/>
+      <c r="L118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:12">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
-      <c r="F119" s="4"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="6"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:10">
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="4"/>
+      <c r="K119" s="5"/>
+      <c r="L119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:12">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
-      <c r="F120" s="4"/>
-      <c r="I120" s="5"/>
-      <c r="J120" s="6"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:10">
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="4"/>
+      <c r="K120" s="5"/>
+      <c r="L120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:12">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="4"/>
-      <c r="I121" s="5"/>
-      <c r="J121" s="6"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:10">
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="4"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:12">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="4"/>
-      <c r="I122" s="5"/>
-      <c r="J122" s="6"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:10">
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="4"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:12">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="4"/>
-      <c r="I123" s="5"/>
-      <c r="J123" s="6"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:10">
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="4"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:12">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="4"/>
-      <c r="I124" s="5"/>
-      <c r="J124" s="6"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:10">
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="4"/>
+      <c r="K124" s="5"/>
+      <c r="L124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:12">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="4"/>
-      <c r="I125" s="5"/>
-      <c r="J125" s="6"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:10">
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="4"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:12">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
-      <c r="F126" s="4"/>
-      <c r="I126" s="5"/>
-      <c r="J126" s="6"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:10">
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="4"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:12">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
-      <c r="F127" s="4"/>
-      <c r="I127" s="5"/>
-      <c r="J127" s="6"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:10">
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="4"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:12">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
-      <c r="F128" s="4"/>
-      <c r="I128" s="5"/>
-      <c r="J128" s="6"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:10">
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="4"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:12">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="4"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
       <c r="H129" s="4"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="6"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:10">
+      <c r="J129" s="4"/>
+      <c r="K129" s="5"/>
+      <c r="L129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:12">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
-      <c r="F130" s="4"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
       <c r="H130" s="4"/>
-      <c r="I130" s="5"/>
-      <c r="J130" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:10">
+      <c r="J130" s="4"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="4"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
       <c r="H131" s="4"/>
-      <c r="I131" s="5"/>
-      <c r="J131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:10">
+      <c r="J131" s="4"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:12">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="4"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
       <c r="H132" s="4"/>
-      <c r="I132" s="5"/>
-      <c r="J132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:10">
+      <c r="J132" s="4"/>
+      <c r="K132" s="5"/>
+      <c r="L132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:12">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="4"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
       <c r="H133" s="4"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="6"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:10">
+      <c r="J133" s="4"/>
+      <c r="K133" s="5"/>
+      <c r="L133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:12">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="4"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
       <c r="H134" s="4"/>
-      <c r="I134" s="5"/>
-      <c r="J134" s="6"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:10">
+      <c r="J134" s="4"/>
+      <c r="K134" s="5"/>
+      <c r="L134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:12">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="4"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
       <c r="H135" s="4"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="6"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:10">
+      <c r="J135" s="4"/>
+      <c r="K135" s="5"/>
+      <c r="L135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="4"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
       <c r="H136" s="4"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="6"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:10">
+      <c r="J136" s="4"/>
+      <c r="K136" s="5"/>
+      <c r="L136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="4"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
       <c r="H137" s="4"/>
-      <c r="I137" s="5"/>
-      <c r="J137" s="6"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:10">
+      <c r="J137" s="4"/>
+      <c r="K137" s="5"/>
+      <c r="L137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="4"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
       <c r="H138" s="4"/>
-      <c r="I138" s="5"/>
-      <c r="J138" s="6"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:10">
+      <c r="J138" s="4"/>
+      <c r="K138" s="5"/>
+      <c r="L138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
-      <c r="F139" s="4"/>
-      <c r="I139" s="5"/>
-      <c r="J139" s="6"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:10">
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="4"/>
+      <c r="K139" s="5"/>
+      <c r="L139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="4"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="6"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:10">
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="4"/>
+      <c r="K140" s="5"/>
+      <c r="L140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:12">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
-      <c r="F141" s="4"/>
-      <c r="I141" s="5"/>
-      <c r="J141" s="6"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:10">
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="4"/>
+      <c r="K141" s="5"/>
+      <c r="L141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:12">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
-      <c r="F142" s="4"/>
-      <c r="I142" s="5"/>
-      <c r="J142" s="6"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:10">
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="4"/>
+      <c r="K142" s="5"/>
+      <c r="L142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:12">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="4"/>
-      <c r="I143" s="5"/>
-      <c r="J143" s="6"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:10">
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="4"/>
+      <c r="K143" s="5"/>
+      <c r="L143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:12">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
-      <c r="F144" s="4"/>
-      <c r="I144" s="5"/>
-      <c r="J144" s="6"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:10">
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="4"/>
+      <c r="K144" s="5"/>
+      <c r="L144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:12">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
-      <c r="F145" s="4"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="6"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:10">
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="4"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:12">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
-      <c r="F146" s="4"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="6"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:10">
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="4"/>
+      <c r="K146" s="5"/>
+      <c r="L146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:12">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
-      <c r="F147" s="4"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="6"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:10">
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="4"/>
+      <c r="K147" s="5"/>
+      <c r="L147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:12">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
-      <c r="F148" s="4"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="6"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:10">
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="4"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:12">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
-      <c r="F149" s="4"/>
-      <c r="I149" s="5"/>
-      <c r="J149" s="6"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:10">
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="4"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:12">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="4"/>
-      <c r="I150" s="5"/>
-      <c r="J150" s="6"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:10">
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="4"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:12">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
-      <c r="F151" s="4"/>
-      <c r="I151" s="5"/>
-      <c r="J151" s="6"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:10">
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="4"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:12">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
-      <c r="F152" s="4"/>
-      <c r="I152" s="5"/>
-      <c r="J152" s="6"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:10">
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="4"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:12">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="4"/>
-      <c r="I153" s="5"/>
-      <c r="J153" s="6"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:10">
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="4"/>
+      <c r="K153" s="5"/>
+      <c r="L153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:12">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="4"/>
-      <c r="I154" s="5"/>
-      <c r="J154" s="6"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:10">
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="4"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
-      <c r="F155" s="4"/>
-      <c r="I155" s="5"/>
-      <c r="J155" s="6"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:10">
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="4"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:12">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
-      <c r="F156" s="4"/>
-      <c r="I156" s="5"/>
-      <c r="J156" s="6"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:10">
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="4"/>
+      <c r="K156" s="5"/>
+      <c r="L156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:12">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
-      <c r="F157" s="4"/>
-      <c r="I157" s="5"/>
-      <c r="J157" s="6"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:10">
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="4"/>
+      <c r="K157" s="5"/>
+      <c r="L157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:12">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
-      <c r="F158" s="4"/>
-      <c r="I158" s="5"/>
-      <c r="J158" s="6"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="4"/>
+      <c r="K158" s="5"/>
+      <c r="L158" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>序号</t>
   </si>
@@ -74,9 +74,6 @@
     <t>多语言ID</t>
   </si>
   <si>
-    <t>需求激活道具ID</t>
-  </si>
-  <si>
     <t>是否开启</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
   </si>
   <si>
     <t>MedalNameId</t>
-  </si>
-  <si>
-    <t>NeedItemId</t>
   </si>
   <si>
     <t>IsOpen</t>
@@ -1582,23 +1576,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.725" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.175" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="20.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24" style="1" customWidth="1"/>
-    <col min="12" max="12" width="32" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.175" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1614,2843 +1608,2557 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:13">
+      <c r="K1" s="5"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:13">
+      <c r="K2" s="5"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:13">
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:13">
+      <c r="K4" s="5"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="8">
-        <v>1001</v>
+        <v>1150001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
         <v>1150001</v>
       </c>
-      <c r="E5" s="3">
-        <v>1150001</v>
-      </c>
-      <c r="F5" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:13">
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="3">
-        <v>1002</v>
+        <v>1150002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3">
         <v>1150002</v>
       </c>
-      <c r="E6" s="3">
-        <v>1150002</v>
-      </c>
-      <c r="F6" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:13">
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
       <c r="A7" s="3">
-        <v>1003</v>
+        <v>1150003</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3">
         <v>1150003</v>
       </c>
-      <c r="E7" s="3">
-        <v>1150003</v>
-      </c>
-      <c r="F7" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:13">
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
       <c r="A8" s="3">
-        <v>1004</v>
+        <v>1150004</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3">
         <v>1150004</v>
       </c>
-      <c r="E8" s="3">
-        <v>1150004</v>
-      </c>
-      <c r="F8" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:13">
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
       <c r="A9" s="3">
-        <v>1005</v>
+        <v>1150005</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3">
         <v>1150005</v>
       </c>
-      <c r="E9" s="3">
-        <v>1150005</v>
-      </c>
-      <c r="F9" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:13">
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
       <c r="A10" s="3">
-        <v>1006</v>
+        <v>1150006</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3">
         <v>1150006</v>
       </c>
-      <c r="E10" s="3">
-        <v>1150006</v>
-      </c>
-      <c r="F10" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:13">
+      <c r="K10" s="5"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="3">
-        <v>1007</v>
+        <v>1150007</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3">
         <v>1150007</v>
       </c>
-      <c r="E11" s="3">
-        <v>1150007</v>
-      </c>
-      <c r="F11" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:13">
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
       <c r="A12" s="3">
-        <v>1008</v>
+        <v>1150008</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3">
         <v>1150008</v>
       </c>
-      <c r="E12" s="3">
-        <v>1150008</v>
-      </c>
-      <c r="F12" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:13">
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
       <c r="A13" s="3">
-        <v>1009</v>
+        <v>1150009</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
         <v>1150009</v>
       </c>
-      <c r="E13" s="3">
-        <v>1150009</v>
-      </c>
-      <c r="F13" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
+      <c r="K13" s="5"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
       <c r="A14" s="3">
-        <v>1010</v>
+        <v>1150010</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
         <v>1150010</v>
       </c>
-      <c r="E14" s="3">
-        <v>1150010</v>
-      </c>
-      <c r="F14" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:13">
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
       <c r="A15" s="3">
-        <v>1011</v>
+        <v>1150011</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="3">
         <v>1150011</v>
       </c>
-      <c r="E15" s="3">
-        <v>1150011</v>
-      </c>
-      <c r="F15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3"/>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:13">
+      <c r="J15" s="5"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
       <c r="A16" s="3">
-        <v>1012</v>
+        <v>1150012</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3">
         <v>1150012</v>
       </c>
-      <c r="E16" s="3">
-        <v>1150012</v>
-      </c>
-      <c r="F16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3"/>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:12">
+      <c r="J16" s="5"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
       <c r="A17" s="3">
-        <v>1013</v>
+        <v>1150013</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>1150013</v>
       </c>
-      <c r="E17" s="3">
-        <v>1150013</v>
-      </c>
-      <c r="F17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3"/>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
+      <c r="J17" s="5"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="3">
-        <v>1014</v>
+        <v>1150014</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="3">
         <v>1150014</v>
       </c>
-      <c r="E18" s="3">
-        <v>1150014</v>
-      </c>
-      <c r="F18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3"/>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:12">
+      <c r="J18" s="5"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
       <c r="A19" s="3">
-        <v>1015</v>
+        <v>1150015</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="3">
         <v>1150015</v>
       </c>
-      <c r="E19" s="3">
-        <v>1150015</v>
-      </c>
-      <c r="F19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3"/>
+      <c r="E19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:12">
+      <c r="J19" s="5"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
       <c r="A20" s="8">
-        <v>2001</v>
+        <v>1150016</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3">
         <v>1150016</v>
       </c>
-      <c r="E20" s="3">
-        <v>1150016</v>
-      </c>
-      <c r="F20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3"/>
+      <c r="E20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:12">
+      <c r="J20" s="5"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
       <c r="A21" s="8">
-        <v>2002</v>
+        <v>1150017</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D21" s="3">
         <v>1150017</v>
       </c>
-      <c r="E21" s="3">
-        <v>1150017</v>
-      </c>
-      <c r="F21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3"/>
+      <c r="E21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
+      <c r="J21" s="5"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="3">
-        <v>2003</v>
+        <v>1150018</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" s="3">
         <v>1150018</v>
       </c>
-      <c r="E22" s="3">
-        <v>1150018</v>
-      </c>
-      <c r="F22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3"/>
+      <c r="E22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:12">
+      <c r="J22" s="5"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
       <c r="A23" s="3">
-        <v>2004</v>
+        <v>1150019</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" s="3">
         <v>1150019</v>
       </c>
-      <c r="E23" s="3">
-        <v>1150019</v>
-      </c>
-      <c r="F23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3"/>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:12">
+      <c r="J23" s="5"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="3">
-        <v>2005</v>
+        <v>1150020</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="3">
         <v>1150020</v>
       </c>
-      <c r="E24" s="3">
-        <v>1150020</v>
-      </c>
-      <c r="F24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3"/>
+      <c r="E24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
+      <c r="J24" s="5"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
       <c r="A25" s="3">
-        <v>2006</v>
+        <v>1150021</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3">
         <v>1150021</v>
       </c>
-      <c r="E25" s="3">
-        <v>1150021</v>
-      </c>
-      <c r="F25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3"/>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
+      <c r="J25" s="5"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
       <c r="A26" s="3">
-        <v>2007</v>
+        <v>1150022</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3">
         <v>1150022</v>
       </c>
-      <c r="E26" s="3">
-        <v>1150022</v>
-      </c>
-      <c r="F26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3"/>
+      <c r="E26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
+      <c r="J26" s="5"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
       <c r="A27" s="8">
-        <v>2008</v>
+        <v>1150023</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="3">
         <v>1150023</v>
       </c>
-      <c r="E27" s="3">
-        <v>1150023</v>
-      </c>
-      <c r="F27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3"/>
+      <c r="E27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:12">
+      <c r="J27" s="5"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
       <c r="A28" s="3">
-        <v>2009</v>
+        <v>1150024</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3">
         <v>1150024</v>
       </c>
-      <c r="E28" s="3">
-        <v>1150024</v>
-      </c>
-      <c r="F28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3"/>
+      <c r="E28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:12">
+      <c r="J28" s="5"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="3">
-        <v>2010</v>
+        <v>1150025</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3">
         <v>1150025</v>
       </c>
-      <c r="E29" s="3">
-        <v>1150025</v>
-      </c>
-      <c r="F29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3"/>
+      <c r="E29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
+      <c r="J29" s="5"/>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
       <c r="A30" s="8">
-        <v>2011</v>
+        <v>1150026</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D30" s="3">
         <v>1150026</v>
       </c>
-      <c r="E30" s="3">
-        <v>1150026</v>
-      </c>
-      <c r="F30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3"/>
+      <c r="E30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
+      <c r="J30" s="5"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
       <c r="A31" s="8">
-        <v>2012</v>
+        <v>1150027</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3">
         <v>1150027</v>
       </c>
-      <c r="E31" s="3">
-        <v>1150027</v>
-      </c>
-      <c r="F31" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3"/>
+      <c r="E31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:12">
+      <c r="J31" s="5"/>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="8">
-        <v>3001</v>
+        <v>1150028</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D32" s="3">
         <v>1150028</v>
       </c>
-      <c r="E32" s="3">
-        <v>1150028</v>
-      </c>
-      <c r="F32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3"/>
+      <c r="E32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:12">
+      <c r="J32" s="5"/>
+      <c r="K32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="3">
-        <v>3002</v>
+        <v>1150029</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3">
         <v>1150029</v>
       </c>
-      <c r="E33" s="3">
-        <v>1150029</v>
-      </c>
-      <c r="F33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3"/>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:12">
+      <c r="J33" s="5"/>
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="3">
-        <v>3003</v>
+        <v>1150030</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3">
         <v>1150030</v>
       </c>
-      <c r="E34" s="3">
-        <v>1150030</v>
-      </c>
-      <c r="F34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3"/>
+      <c r="E34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:12">
+      <c r="J34" s="5"/>
+      <c r="K34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="3">
-        <v>3004</v>
+        <v>1150031</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3">
         <v>1150031</v>
       </c>
-      <c r="E35" s="3">
-        <v>1150031</v>
-      </c>
-      <c r="F35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3"/>
+      <c r="E35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:12">
+      <c r="J35" s="5"/>
+      <c r="K35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:11">
       <c r="A36" s="8">
-        <v>3005</v>
+        <v>1150032</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3">
         <v>1150032</v>
       </c>
-      <c r="E36" s="3">
-        <v>1150032</v>
-      </c>
-      <c r="F36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="E36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:12">
+      <c r="J36" s="5"/>
+      <c r="K36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:11">
       <c r="A37" s="3">
-        <v>3006</v>
+        <v>1150033</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
         <v>1150033</v>
       </c>
-      <c r="E37" s="3">
-        <v>1150033</v>
-      </c>
-      <c r="F37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3"/>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:12">
+      <c r="J37" s="5"/>
+      <c r="K37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:11">
       <c r="A38" s="3">
-        <v>3007</v>
+        <v>1150034</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3">
         <v>1150034</v>
       </c>
-      <c r="E38" s="3">
-        <v>1150034</v>
-      </c>
-      <c r="F38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3"/>
+      <c r="E38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:12">
+      <c r="J38" s="5"/>
+      <c r="K38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:11">
       <c r="A39" s="3">
-        <v>3008</v>
+        <v>1150035</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3">
         <v>1150035</v>
       </c>
-      <c r="E39" s="3">
-        <v>1150035</v>
-      </c>
-      <c r="F39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3"/>
+      <c r="E39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
+      <c r="J39" s="5"/>
+      <c r="K39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:11">
       <c r="A40" s="3">
-        <v>3009</v>
+        <v>1150036</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3">
         <v>1150036</v>
       </c>
-      <c r="E40" s="3">
-        <v>1150036</v>
-      </c>
-      <c r="F40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3"/>
+      <c r="E40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
+      <c r="J40" s="5"/>
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:11">
       <c r="A41" s="3">
-        <v>3010</v>
+        <v>1150037</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3">
         <v>1150037</v>
       </c>
-      <c r="E41" s="3">
-        <v>1150037</v>
-      </c>
-      <c r="F41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3"/>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
+      <c r="J41" s="5"/>
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:11">
       <c r="A42" s="3">
-        <v>3011</v>
+        <v>1150038</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3">
         <v>1150038</v>
       </c>
-      <c r="E42" s="3">
-        <v>1150038</v>
-      </c>
-      <c r="F42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3"/>
+      <c r="E42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:12">
+      <c r="J42" s="5"/>
+      <c r="K42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:11">
       <c r="A43" s="8">
-        <v>3012</v>
+        <v>1150039</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3">
         <v>1150039</v>
       </c>
-      <c r="E43" s="3">
-        <v>1150039</v>
-      </c>
-      <c r="F43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3"/>
+      <c r="E43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:12">
+      <c r="J43" s="5"/>
+      <c r="K43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:11">
       <c r="A44" s="3">
-        <v>3013</v>
+        <v>1150040</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <v>1150040</v>
       </c>
-      <c r="E44" s="3">
-        <v>1150040</v>
-      </c>
-      <c r="F44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3"/>
+      <c r="E44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:12">
+      <c r="J44" s="5"/>
+      <c r="K44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:11">
       <c r="A45" s="3">
-        <v>3014</v>
+        <v>1150041</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3">
         <v>1150041</v>
       </c>
-      <c r="E45" s="3">
-        <v>1150041</v>
-      </c>
-      <c r="F45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3"/>
+      <c r="E45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:12">
+      <c r="J45" s="5"/>
+      <c r="K45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:11">
       <c r="A46" s="8">
-        <v>4001</v>
+        <v>1150042</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D46" s="3">
         <v>1150042</v>
       </c>
-      <c r="E46" s="3">
-        <v>1150042</v>
-      </c>
-      <c r="F46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3"/>
+      <c r="E46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:12">
+      <c r="J46" s="5"/>
+      <c r="K46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:11">
       <c r="A47" s="3">
-        <v>4002</v>
+        <v>1150043</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3">
         <v>1150043</v>
       </c>
-      <c r="E47" s="3">
-        <v>1150043</v>
-      </c>
-      <c r="F47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3"/>
+      <c r="E47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:12">
+      <c r="J47" s="5"/>
+      <c r="K47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:11">
       <c r="A48" s="3">
-        <v>4003</v>
+        <v>1150044</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3">
         <v>1150044</v>
       </c>
-      <c r="E48" s="3">
-        <v>1150044</v>
-      </c>
-      <c r="F48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3"/>
+      <c r="E48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:12">
+      <c r="J48" s="5"/>
+      <c r="K48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:11">
       <c r="A49" s="3">
-        <v>4004</v>
+        <v>1150045</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3">
         <v>1150045</v>
       </c>
-      <c r="E49" s="3">
-        <v>1150045</v>
-      </c>
-      <c r="F49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3"/>
+      <c r="E49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:12">
+      <c r="J49" s="5"/>
+      <c r="K49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:11">
       <c r="A50" s="3">
-        <v>4005</v>
+        <v>1150046</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3">
         <v>1150046</v>
       </c>
-      <c r="E50" s="3">
-        <v>1150046</v>
-      </c>
-      <c r="F50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3"/>
+      <c r="E50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:12">
+      <c r="J50" s="5"/>
+      <c r="K50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:11">
       <c r="A51" s="3">
-        <v>4006</v>
+        <v>1150047</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3">
         <v>1150047</v>
       </c>
-      <c r="E51" s="3">
-        <v>1150047</v>
-      </c>
-      <c r="F51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3"/>
+      <c r="E51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:12">
+      <c r="J51" s="5"/>
+      <c r="K51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:11">
       <c r="A52" s="8">
-        <v>4007</v>
+        <v>1150048</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3">
         <v>1150048</v>
       </c>
-      <c r="E52" s="3">
-        <v>1150048</v>
-      </c>
-      <c r="F52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3"/>
+      <c r="E52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:12">
+      <c r="J52" s="5"/>
+      <c r="K52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:11">
       <c r="A53" s="3">
-        <v>4008</v>
+        <v>1150049</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3">
         <v>1150049</v>
       </c>
-      <c r="E53" s="3">
-        <v>1150049</v>
-      </c>
-      <c r="F53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3"/>
+      <c r="E53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:12">
+      <c r="J53" s="5"/>
+      <c r="K53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:11">
       <c r="A54" s="3">
-        <v>4009</v>
+        <v>1150050</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3">
         <v>1150050</v>
       </c>
-      <c r="E54" s="3">
-        <v>1150050</v>
-      </c>
-      <c r="F54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3"/>
+      <c r="E54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:12">
+      <c r="J54" s="5"/>
+      <c r="K54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:11">
       <c r="A55" s="3">
-        <v>4010</v>
+        <v>1150051</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3">
         <v>1150051</v>
       </c>
-      <c r="E55" s="3">
-        <v>1150051</v>
-      </c>
-      <c r="F55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3"/>
+      <c r="E55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:12">
+      <c r="J55" s="5"/>
+      <c r="K55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:11">
       <c r="A56" s="3">
-        <v>4011</v>
+        <v>1150052</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3">
         <v>1150052</v>
       </c>
-      <c r="E56" s="3">
-        <v>1150052</v>
-      </c>
-      <c r="F56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3"/>
+      <c r="E56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:12">
+      <c r="J56" s="5"/>
+      <c r="K56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:11">
       <c r="A57" s="3">
-        <v>4012</v>
+        <v>1150053</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3">
         <v>1150053</v>
       </c>
-      <c r="E57" s="3">
-        <v>1150053</v>
-      </c>
-      <c r="F57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3"/>
+      <c r="E57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:12">
+      <c r="J57" s="5"/>
+      <c r="K57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:11">
       <c r="A58" s="8">
-        <v>4013</v>
+        <v>1150054</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3">
         <v>1150054</v>
       </c>
-      <c r="E58" s="3">
-        <v>1150054</v>
-      </c>
-      <c r="F58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3"/>
+      <c r="E58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:12">
+      <c r="J58" s="5"/>
+      <c r="K58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:11">
       <c r="A59" s="3">
-        <v>4014</v>
+        <v>1150055</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
         <v>1150055</v>
       </c>
-      <c r="E59" s="3">
-        <v>1150055</v>
-      </c>
-      <c r="F59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="3"/>
+      <c r="E59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:12">
+      <c r="J59" s="5"/>
+      <c r="K59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:11">
       <c r="A60" s="3">
-        <v>4015</v>
+        <v>1150056</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
         <v>1150056</v>
       </c>
-      <c r="E60" s="3">
-        <v>1150056</v>
-      </c>
-      <c r="F60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="3"/>
+      <c r="E60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:12">
+      <c r="J60" s="5"/>
+      <c r="K60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:11">
       <c r="A61" s="3">
-        <v>4016</v>
+        <v>1150057</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3">
         <v>1150057</v>
       </c>
-      <c r="E61" s="3">
-        <v>1150057</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="6"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:12">
+      <c r="J61" s="5"/>
+      <c r="K61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:11">
       <c r="A62" s="3">
-        <v>4017</v>
+        <v>1150058</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
         <v>1150058</v>
       </c>
-      <c r="E62" s="3">
-        <v>1150058</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:12">
+      <c r="J62" s="5"/>
+      <c r="K62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:11">
       <c r="A63" s="3">
-        <v>4018</v>
+        <v>1150059</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3">
         <v>1150059</v>
       </c>
-      <c r="E63" s="3">
-        <v>1150059</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:12">
+      <c r="J63" s="5"/>
+      <c r="K63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:11">
       <c r="A64" s="3">
-        <v>4019</v>
+        <v>1150060</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3">
         <v>1150060</v>
       </c>
-      <c r="E64" s="3">
-        <v>1150060</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G64" s="3"/>
+      <c r="E64" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:12">
+      <c r="J64" s="5"/>
+      <c r="K64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:11">
       <c r="A65" s="3">
-        <v>4020</v>
+        <v>1150061</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3">
         <v>1150061</v>
       </c>
-      <c r="E65" s="3">
-        <v>1150061</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G65" s="3"/>
+      <c r="E65" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:12">
+      <c r="J65" s="5"/>
+      <c r="K65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:11">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:12">
+      <c r="J66" s="5"/>
+      <c r="K66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:11">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:12">
+      <c r="J67" s="5"/>
+      <c r="K67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:11">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:12">
+      <c r="J68" s="5"/>
+      <c r="K68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:11">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:12">
+      <c r="J69" s="5"/>
+      <c r="K69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:11">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:12">
+      <c r="J70" s="5"/>
+      <c r="K70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:11">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:12">
+      <c r="J71" s="5"/>
+      <c r="K71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:11">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
+      <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="6"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:12">
+      <c r="J72" s="5"/>
+      <c r="K72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:11">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:12">
+      <c r="J73" s="5"/>
+      <c r="K73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:11">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
+      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:12">
+      <c r="J74" s="5"/>
+      <c r="K74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:11">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:12">
+      <c r="J75" s="5"/>
+      <c r="K75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:11">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:12">
+      <c r="J76" s="5"/>
+      <c r="K76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:11">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
+      <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:12">
+      <c r="J77" s="5"/>
+      <c r="K77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:11">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
+      <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:12">
+      <c r="J78" s="5"/>
+      <c r="K78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
+      <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:12">
+      <c r="J79" s="5"/>
+      <c r="K79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
+      <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:12">
+      <c r="J80" s="5"/>
+      <c r="K80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:12">
+      <c r="J81" s="5"/>
+      <c r="K81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
+      <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:12">
+      <c r="J82" s="5"/>
+      <c r="K82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
+      <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:12">
+      <c r="J83" s="5"/>
+      <c r="K83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
+      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:12">
+      <c r="J84" s="5"/>
+      <c r="K84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
+      <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:12">
+      <c r="J85" s="5"/>
+      <c r="K85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:12">
+      <c r="J86" s="5"/>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
+      <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="5"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:12">
+      <c r="J87" s="5"/>
+      <c r="K87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
+      <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="5"/>
-      <c r="L88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:12">
+      <c r="J88" s="5"/>
+      <c r="K88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:11">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="6"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:12">
+      <c r="J89" s="5"/>
+      <c r="K89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:11">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="6"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:12">
+      <c r="J90" s="5"/>
+      <c r="K90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:12">
+      <c r="J91" s="5"/>
+      <c r="K91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
+      <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:12">
+      <c r="J92" s="5"/>
+      <c r="K92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:11">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
+      <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:12">
+      <c r="J93" s="5"/>
+      <c r="K93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:11">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+      <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:12">
+      <c r="J94" s="5"/>
+      <c r="K94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:11">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+      <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="6"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:12">
+      <c r="J95" s="5"/>
+      <c r="K95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:11">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+      <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="6"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:12">
+      <c r="J96" s="5"/>
+      <c r="K96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:11">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
+      <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="6"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:12">
+      <c r="J97" s="5"/>
+      <c r="K97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
+      <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:12">
+      <c r="J98" s="5"/>
+      <c r="K98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:11">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
+      <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
+      <c r="J99" s="5"/>
+      <c r="K99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:11">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:12">
+      <c r="J100" s="5"/>
+      <c r="K100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:11">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:12">
+      <c r="J101" s="5"/>
+      <c r="K101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:11">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
+      <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:12">
+      <c r="J102" s="5"/>
+      <c r="K102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:11">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
+      <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="6"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:12">
+      <c r="J103" s="5"/>
+      <c r="K103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:11">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
+      <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:12">
+      <c r="J104" s="5"/>
+      <c r="K104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:11">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
+      <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:12">
+      <c r="J105" s="5"/>
+      <c r="K105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:11">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
+      <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:12">
+      <c r="J106" s="5"/>
+      <c r="K106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:11">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
+      <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:12">
+      <c r="J107" s="5"/>
+      <c r="K107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:11">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
+      <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="5"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:12">
+      <c r="J108" s="5"/>
+      <c r="K108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:11">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
+      <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:12">
+      <c r="J109" s="5"/>
+      <c r="K109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:11">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
+      <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:12">
+      <c r="J110" s="5"/>
+      <c r="K110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:11">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
+      <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:12">
+      <c r="J111" s="5"/>
+      <c r="K111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:11">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
+      <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:12">
+      <c r="J112" s="5"/>
+      <c r="K112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:11">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
+      <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:12">
+      <c r="J113" s="5"/>
+      <c r="K113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:11">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
+      <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="6"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:12">
+      <c r="J114" s="5"/>
+      <c r="K114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:11">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
+      <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="6"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:12">
+      <c r="J115" s="5"/>
+      <c r="K115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:11">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
+      <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="6"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:12">
+      <c r="J116" s="5"/>
+      <c r="K116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:11">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
+      <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="6"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:12">
+      <c r="J117" s="5"/>
+      <c r="K117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:11">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
+      <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="6"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:12">
+      <c r="J118" s="5"/>
+      <c r="K118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:11">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="4"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="6"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:12">
+      <c r="G119" s="4"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="4"/>
-      <c r="K120" s="5"/>
-      <c r="L120" s="6"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:12">
+      <c r="G120" s="4"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="4"/>
-      <c r="K121" s="5"/>
-      <c r="L121" s="6"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:12">
+      <c r="G121" s="4"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="4"/>
-      <c r="K122" s="5"/>
-      <c r="L122" s="6"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:12">
+      <c r="G122" s="4"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="4"/>
-      <c r="K123" s="5"/>
-      <c r="L123" s="6"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:12">
+      <c r="G123" s="4"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="4"/>
-      <c r="K124" s="5"/>
-      <c r="L124" s="6"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:12">
+      <c r="G124" s="4"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="4"/>
-      <c r="K125" s="5"/>
-      <c r="L125" s="6"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:12">
+      <c r="G125" s="4"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="4"/>
-      <c r="K126" s="5"/>
-      <c r="L126" s="6"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:12">
+      <c r="G126" s="4"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="4"/>
-      <c r="K127" s="5"/>
-      <c r="L127" s="6"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:12">
+      <c r="G127" s="4"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="4"/>
-      <c r="K128" s="5"/>
-      <c r="L128" s="6"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:12">
+      <c r="G128" s="4"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="6"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:12">
+      <c r="G129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:11">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:12">
+      <c r="G130" s="4"/>
+      <c r="I130" s="4"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:11">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:12">
+      <c r="G131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:11">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="5"/>
-      <c r="L132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:12">
+      <c r="G132" s="4"/>
+      <c r="I132" s="4"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:11">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="6"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:12">
+      <c r="G133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:11">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
-      <c r="G134" s="3"/>
-      <c r="H134" s="4"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="6"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:12">
+      <c r="G134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:11">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="6"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:12">
+      <c r="G135" s="4"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:11">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-      <c r="G136" s="3"/>
-      <c r="H136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="6"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:12">
+      <c r="G136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:11">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="6"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:12">
+      <c r="G137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:11">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="6"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:12">
+      <c r="G138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:11">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="4"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="6"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:12">
+      <c r="G139" s="4"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:11">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="4"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="6"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:12">
+      <c r="G140" s="4"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:11">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
-      <c r="G141" s="3"/>
-      <c r="H141" s="4"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="6"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:12">
+      <c r="G141" s="4"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:11">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="4"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="6"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:12">
+      <c r="G142" s="4"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:11">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="4"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="6"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:12">
+      <c r="G143" s="4"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:11">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-      <c r="G144" s="3"/>
-      <c r="H144" s="4"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="6"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:12">
+      <c r="G144" s="4"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:11">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="4"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="6"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:12">
+      <c r="G145" s="4"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:11">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="4"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="6"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:12">
+      <c r="G146" s="4"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:11">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="4"/>
-      <c r="K147" s="5"/>
-      <c r="L147" s="6"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:12">
+      <c r="G147" s="4"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:11">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="4"/>
-      <c r="K148" s="5"/>
-      <c r="L148" s="6"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:12">
+      <c r="G148" s="4"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:11">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
-      <c r="G149" s="3"/>
-      <c r="H149" s="4"/>
-      <c r="K149" s="5"/>
-      <c r="L149" s="6"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:12">
+      <c r="G149" s="4"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:11">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
-      <c r="G150" s="3"/>
-      <c r="H150" s="4"/>
-      <c r="K150" s="5"/>
-      <c r="L150" s="6"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:12">
+      <c r="G150" s="4"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:11">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
-      <c r="G151" s="3"/>
-      <c r="H151" s="4"/>
-      <c r="K151" s="5"/>
-      <c r="L151" s="6"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:12">
+      <c r="G151" s="4"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
-      <c r="G152" s="3"/>
-      <c r="H152" s="4"/>
-      <c r="K152" s="5"/>
-      <c r="L152" s="6"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:12">
+      <c r="G152" s="4"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:11">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
-      <c r="G153" s="3"/>
-      <c r="H153" s="4"/>
-      <c r="K153" s="5"/>
-      <c r="L153" s="6"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:12">
+      <c r="G153" s="4"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:11">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
-      <c r="G154" s="3"/>
-      <c r="H154" s="4"/>
-      <c r="K154" s="5"/>
-      <c r="L154" s="6"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:12">
+      <c r="G154" s="4"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
-      <c r="G155" s="3"/>
-      <c r="H155" s="4"/>
-      <c r="K155" s="5"/>
-      <c r="L155" s="6"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:12">
+      <c r="G155" s="4"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
-      <c r="G156" s="3"/>
-      <c r="H156" s="4"/>
-      <c r="K156" s="5"/>
-      <c r="L156" s="6"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:12">
+      <c r="G156" s="4"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
-      <c r="G157" s="3"/>
-      <c r="H157" s="4"/>
-      <c r="K157" s="5"/>
-      <c r="L157" s="6"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:12">
+      <c r="G157" s="4"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
-      <c r="G158" s="3"/>
-      <c r="H158" s="4"/>
-      <c r="K158" s="5"/>
-      <c r="L158" s="6"/>
+      <c r="G158" s="4"/>
+      <c r="J158" s="5"/>
+      <c r="K158" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -32,7 +32,32 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 白银
+2. 钻石
+3. 铂金
+4. 彩金</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
   <si>
     <t>序号</t>
   </si>
@@ -71,6 +96,9 @@
     <t>#对应任务</t>
   </si>
   <si>
+    <t>品质</t>
+  </si>
+  <si>
     <t>多语言ID</t>
   </si>
   <si>
@@ -84,6 +112,9 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>Quality</t>
   </si>
   <si>
     <t>MedalNameId</t>
@@ -1576,23 +1607,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.725" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.175" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="20.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24" style="1" customWidth="1"/>
-    <col min="11" max="11" width="32" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="7.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.175" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="20.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24" style="1" customWidth="1"/>
+    <col min="12" max="12" width="32" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1608,2557 +1640,2843 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:12">
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:12">
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:12">
+      <c r="K3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="3"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:12">
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:13">
       <c r="A5" s="8">
         <v>1150001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
         <v>1150001</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:12">
+      <c r="K5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:13">
       <c r="A6" s="3">
         <v>1150002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
         <v>1150002</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:12">
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:13">
       <c r="A7" s="3">
         <v>1150003</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
         <v>1150003</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:12">
+      <c r="K7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
       <c r="A8" s="3">
         <v>1150004</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
         <v>1150004</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:12">
+      <c r="K8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
       <c r="A9" s="3">
         <v>1150005</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
         <v>1150005</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:12">
+      <c r="K9" s="4"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
       <c r="A10" s="3">
         <v>1150006</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
         <v>1150006</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:12">
+      <c r="K10" s="4"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
       <c r="A11" s="3">
         <v>1150007</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
         <v>1150007</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:12">
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
       <c r="A12" s="3">
         <v>1150008</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
         <v>1150008</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
+      <c r="H12" s="3"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:12">
+      <c r="K12" s="4"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
       <c r="A13" s="3">
         <v>1150009</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
         <v>1150009</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:12">
+      <c r="K13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
       <c r="A14" s="3">
         <v>1150010</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
         <v>1150010</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:12">
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
       <c r="A15" s="3">
         <v>1150011</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
         <v>1150011</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
+      <c r="F15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:12">
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
       <c r="A16" s="3">
         <v>1150012</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
         <v>1150012</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
+      <c r="F16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
+      <c r="J16" s="4"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
       <c r="A17" s="3">
         <v>1150013</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
         <v>1150013</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
+      <c r="F17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
+      <c r="J17" s="4"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
       <c r="A18" s="3">
         <v>1150014</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
         <v>1150014</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
+      <c r="F18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:11">
+      <c r="J18" s="4"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
       <c r="A19" s="3">
         <v>1150015</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
         <v>1150015</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
+      <c r="F19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:11">
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
       <c r="A20" s="8">
         <v>1150016</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3">
         <v>1150016</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
+      <c r="F20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:11">
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
       <c r="A21" s="8">
         <v>1150017</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3">
         <v>1150017</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
+      <c r="F21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
+      <c r="J21" s="4"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
       <c r="A22" s="3">
         <v>1150018</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D22" s="3">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3">
         <v>1150018</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
+      <c r="F22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
       <c r="A23" s="3">
         <v>1150019</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3">
         <v>1150019</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
+      <c r="F23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
       <c r="A24" s="3">
         <v>1150020</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3">
         <v>1150020</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
+      <c r="F24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
       <c r="A25" s="3">
         <v>1150021</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3">
         <v>1150021</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
+      <c r="F25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:11">
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
       <c r="A26" s="3">
         <v>1150022</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3">
         <v>1150022</v>
       </c>
-      <c r="E26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
+      <c r="F26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:11">
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
       <c r="A27" s="8">
         <v>1150023</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27" s="3">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3">
         <v>1150023</v>
       </c>
-      <c r="E27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
+      <c r="F27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
       <c r="A28" s="3">
         <v>1150024</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3">
         <v>1150024</v>
       </c>
-      <c r="E28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
+      <c r="F28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
       <c r="A29" s="3">
         <v>1150025</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3">
         <v>1150025</v>
       </c>
-      <c r="E29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
+      <c r="F29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
       <c r="A30" s="8">
         <v>1150026</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3">
         <v>1150026</v>
       </c>
-      <c r="E30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
+      <c r="F30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:11">
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
       <c r="A31" s="8">
         <v>1150027</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
         <v>1150027</v>
       </c>
-      <c r="E31" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
+      <c r="F31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:11">
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
       <c r="A32" s="8">
         <v>1150028</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D32" s="3">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>1150028</v>
       </c>
-      <c r="E32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
+      <c r="F32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:11">
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:12">
       <c r="A33" s="3">
         <v>1150029</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" s="3">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
         <v>1150029</v>
       </c>
-      <c r="E33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
+      <c r="F33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:11">
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:12">
       <c r="A34" s="3">
         <v>1150030</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3">
         <v>1150030</v>
       </c>
-      <c r="E34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="4"/>
+      <c r="F34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:11">
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:12">
       <c r="A35" s="3">
         <v>1150031</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
         <v>1150031</v>
       </c>
-      <c r="E35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
+      <c r="F35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:11">
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:12">
       <c r="A36" s="8">
         <v>1150032</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3">
+        <v>3</v>
+      </c>
+      <c r="E36" s="3">
         <v>1150032</v>
       </c>
-      <c r="E36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="4"/>
+      <c r="F36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:11">
+      <c r="J36" s="4"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
       <c r="A37" s="3">
         <v>1150033</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
+        <v>3</v>
+      </c>
+      <c r="E37" s="3">
         <v>1150033</v>
       </c>
-      <c r="E37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="4"/>
+      <c r="F37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:11">
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
       <c r="A38" s="3">
         <v>1150034</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3">
+        <v>3</v>
+      </c>
+      <c r="E38" s="3">
         <v>1150034</v>
       </c>
-      <c r="E38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="4"/>
+      <c r="F38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="6"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:11">
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
       <c r="A39" s="3">
         <v>1150035</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3">
+        <v>3</v>
+      </c>
+      <c r="E39" s="3">
         <v>1150035</v>
       </c>
-      <c r="E39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="4"/>
+      <c r="F39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="6"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:11">
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
       <c r="A40" s="3">
         <v>1150036</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3">
         <v>1150036</v>
       </c>
-      <c r="E40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="4"/>
+      <c r="F40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:11">
+      <c r="J40" s="4"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
       <c r="A41" s="3">
         <v>1150037</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
         <v>1150037</v>
       </c>
-      <c r="E41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="4"/>
+      <c r="F41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:11">
+      <c r="J41" s="4"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
       <c r="A42" s="3">
         <v>1150038</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3">
         <v>1150038</v>
       </c>
-      <c r="E42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="4"/>
+      <c r="F42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:11">
+      <c r="J42" s="4"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
       <c r="A43" s="8">
         <v>1150039</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>1150039</v>
       </c>
-      <c r="E43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="4"/>
+      <c r="F43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:11">
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
       <c r="A44" s="3">
         <v>1150040</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>1150040</v>
       </c>
-      <c r="E44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="4"/>
+      <c r="F44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:11">
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
       <c r="A45" s="3">
         <v>1150041</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>1150041</v>
       </c>
-      <c r="E45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="4"/>
+      <c r="F45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="6"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:11">
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
       <c r="A46" s="8">
         <v>1150042</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D46" s="3">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
         <v>1150042</v>
       </c>
-      <c r="E46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="4"/>
+      <c r="F46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:11">
+      <c r="J46" s="4"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
       <c r="A47" s="3">
         <v>1150043</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>1150043</v>
       </c>
-      <c r="E47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="4"/>
+      <c r="F47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:11">
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:12">
       <c r="A48" s="3">
         <v>1150044</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>1150044</v>
       </c>
-      <c r="E48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="4"/>
+      <c r="F48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:11">
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:12">
       <c r="A49" s="3">
         <v>1150045</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3">
         <v>1150045</v>
       </c>
-      <c r="E49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="4"/>
+      <c r="F49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:11">
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:12">
       <c r="A50" s="3">
         <v>1150046</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3">
+        <v>4</v>
+      </c>
+      <c r="E50" s="3">
         <v>1150046</v>
       </c>
-      <c r="E50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="4"/>
+      <c r="F50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="6"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:11">
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:12">
       <c r="A51" s="3">
         <v>1150047</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3">
+        <v>4</v>
+      </c>
+      <c r="E51" s="3">
         <v>1150047</v>
       </c>
-      <c r="E51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="4"/>
+      <c r="F51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:11">
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:12">
       <c r="A52" s="8">
         <v>1150048</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>1150048</v>
       </c>
-      <c r="E52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="4"/>
+      <c r="F52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:11">
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:12">
       <c r="A53" s="3">
         <v>1150049</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3">
+        <v>4</v>
+      </c>
+      <c r="E53" s="3">
         <v>1150049</v>
       </c>
-      <c r="E53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="4"/>
+      <c r="F53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:11">
+      <c r="J53" s="4"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:12">
       <c r="A54" s="3">
         <v>1150050</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3">
         <v>1150050</v>
       </c>
-      <c r="E54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="4"/>
+      <c r="F54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:11">
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:12">
       <c r="A55" s="3">
         <v>1150051</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3">
+        <v>4</v>
+      </c>
+      <c r="E55" s="3">
         <v>1150051</v>
       </c>
-      <c r="E55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="4"/>
+      <c r="F55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="6"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:11">
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:12">
       <c r="A56" s="3">
         <v>1150052</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3">
+        <v>4</v>
+      </c>
+      <c r="E56" s="3">
         <v>1150052</v>
       </c>
-      <c r="E56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="4"/>
+      <c r="F56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="6"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:11">
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:12">
       <c r="A57" s="3">
         <v>1150053</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
         <v>1150053</v>
       </c>
-      <c r="E57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="4"/>
+      <c r="F57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:11">
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:12">
       <c r="A58" s="8">
         <v>1150054</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3">
         <v>1150054</v>
       </c>
-      <c r="E58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="4"/>
+      <c r="F58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:11">
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:12">
       <c r="A59" s="3">
         <v>1150055</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>1150055</v>
       </c>
-      <c r="E59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="4"/>
+      <c r="F59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:11">
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:12">
       <c r="A60" s="3">
         <v>1150056</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>1150056</v>
       </c>
-      <c r="E60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="4"/>
+      <c r="F60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="6"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:11">
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
       <c r="A61" s="3">
         <v>1150057</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3">
+        <v>4</v>
+      </c>
+      <c r="E61" s="3">
         <v>1150057</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="4"/>
+      <c r="F61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" s="3"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="6"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:11">
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
       <c r="A62" s="3">
         <v>1150058</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
         <v>1150058</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="4"/>
+      <c r="F62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:11">
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
       <c r="A63" s="3">
         <v>1150059</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3">
+        <v>4</v>
+      </c>
+      <c r="E63" s="3">
         <v>1150059</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="4"/>
+      <c r="F63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:11">
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
       <c r="A64" s="3">
         <v>1150060</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3">
+        <v>4</v>
+      </c>
+      <c r="E64" s="3">
         <v>1150060</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="4"/>
+      <c r="F64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:11">
+      <c r="J64" s="4"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:12">
       <c r="A65" s="3">
         <v>1150061</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3">
+        <v>4</v>
+      </c>
+      <c r="E65" s="3">
         <v>1150061</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="4"/>
+      <c r="F65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:11">
+      <c r="J65" s="4"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:12">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="4"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:11">
+      <c r="J66" s="4"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:12">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="4"/>
+      <c r="G67" s="3"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:11">
+      <c r="J67" s="4"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:12">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="4"/>
+      <c r="G68" s="3"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:11">
+      <c r="J68" s="4"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:12">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="4"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:11">
+      <c r="J69" s="4"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:12">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="4"/>
+      <c r="G70" s="3"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:11">
+      <c r="J70" s="4"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:12">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="4"/>
+      <c r="G71" s="3"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:11">
+      <c r="J71" s="4"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:12">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="4"/>
+      <c r="G72" s="3"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="6"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:11">
+      <c r="J72" s="4"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:12">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="4"/>
+      <c r="G73" s="3"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:11">
+      <c r="J73" s="4"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:12">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="4"/>
+      <c r="G74" s="3"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:11">
+      <c r="J74" s="4"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:12">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="4"/>
+      <c r="G75" s="3"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:11">
+      <c r="J75" s="4"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:12">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="4"/>
+      <c r="G76" s="3"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:11">
+      <c r="J76" s="4"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:12">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="4"/>
+      <c r="G77" s="3"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:11">
+      <c r="J77" s="4"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:12">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="4"/>
+      <c r="G78" s="3"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:11">
+      <c r="J78" s="4"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:12">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="4"/>
+      <c r="G79" s="3"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:11">
+      <c r="J79" s="4"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:12">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="4"/>
+      <c r="G80" s="3"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:11">
+      <c r="J80" s="4"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:12">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="4"/>
+      <c r="G81" s="3"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:11">
+      <c r="J81" s="4"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:12">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="4"/>
+      <c r="G82" s="3"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:11">
+      <c r="J82" s="4"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:12">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="4"/>
+      <c r="G83" s="3"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:11">
+      <c r="J83" s="4"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:12">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="4"/>
+      <c r="G84" s="3"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:11">
+      <c r="J84" s="4"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:12">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="4"/>
+      <c r="G85" s="3"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="5"/>
-      <c r="K85" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:11">
+      <c r="J85" s="4"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="4"/>
+      <c r="G86" s="3"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="5"/>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:11">
+      <c r="J86" s="4"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="4"/>
+      <c r="G87" s="3"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:11">
+      <c r="J87" s="4"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:12">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="4"/>
+      <c r="G88" s="3"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:11">
+      <c r="J88" s="4"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:12">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="4"/>
+      <c r="G89" s="3"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="6"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:11">
+      <c r="J89" s="4"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:12">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="4"/>
+      <c r="G90" s="3"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="6"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:11">
+      <c r="J90" s="4"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="4"/>
+      <c r="G91" s="3"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:11">
+      <c r="J91" s="4"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="4"/>
+      <c r="G92" s="3"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:11">
+      <c r="J92" s="4"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="4"/>
+      <c r="G93" s="3"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:11">
+      <c r="J93" s="4"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:12">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
-      <c r="G94" s="4"/>
+      <c r="G94" s="3"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:11">
+      <c r="J94" s="4"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:12">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-      <c r="G95" s="4"/>
+      <c r="G95" s="3"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="6"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:11">
+      <c r="J95" s="4"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:12">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
-      <c r="G96" s="4"/>
+      <c r="G96" s="3"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="6"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:11">
+      <c r="J96" s="4"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:12">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="4"/>
+      <c r="G97" s="3"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="6"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:11">
+      <c r="J97" s="4"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:12">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="4"/>
+      <c r="G98" s="3"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:11">
+      <c r="J98" s="4"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:12">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
-      <c r="G99" s="4"/>
+      <c r="G99" s="3"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:11">
+      <c r="J99" s="4"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
-      <c r="G100" s="4"/>
+      <c r="G100" s="3"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:11">
+      <c r="J100" s="4"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
-      <c r="G101" s="4"/>
+      <c r="G101" s="3"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:11">
+      <c r="J101" s="4"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
-      <c r="G102" s="4"/>
+      <c r="G102" s="3"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:11">
+      <c r="J102" s="4"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
-      <c r="G103" s="4"/>
+      <c r="G103" s="3"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="6"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:11">
+      <c r="J103" s="4"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
-      <c r="G104" s="4"/>
+      <c r="G104" s="3"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="6"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:11">
+      <c r="J104" s="4"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
-      <c r="G105" s="4"/>
+      <c r="G105" s="3"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:11">
+      <c r="J105" s="4"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:12">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
-      <c r="G106" s="4"/>
+      <c r="G106" s="3"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:11">
+      <c r="J106" s="4"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:12">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
-      <c r="G107" s="4"/>
+      <c r="G107" s="3"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="5"/>
-      <c r="K107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:11">
+      <c r="J107" s="4"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:12">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
-      <c r="G108" s="4"/>
+      <c r="G108" s="3"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="5"/>
-      <c r="K108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:11">
+      <c r="J108" s="4"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:12">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
-      <c r="G109" s="4"/>
+      <c r="G109" s="3"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:11">
+      <c r="J109" s="4"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:12">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
-      <c r="G110" s="4"/>
+      <c r="G110" s="3"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:11">
+      <c r="J110" s="4"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:12">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
-      <c r="G111" s="4"/>
+      <c r="G111" s="3"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:11">
+      <c r="J111" s="4"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:12">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
-      <c r="G112" s="4"/>
+      <c r="G112" s="3"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:11">
+      <c r="J112" s="4"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:12">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
-      <c r="G113" s="4"/>
+      <c r="G113" s="3"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:11">
+      <c r="J113" s="4"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:12">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
-      <c r="G114" s="4"/>
+      <c r="G114" s="3"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="6"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:11">
+      <c r="J114" s="4"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:12">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
-      <c r="G115" s="4"/>
+      <c r="G115" s="3"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="6"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:11">
+      <c r="J115" s="4"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:12">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
-      <c r="G116" s="4"/>
+      <c r="G116" s="3"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="6"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:11">
+      <c r="J116" s="4"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:12">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
-      <c r="G117" s="4"/>
+      <c r="G117" s="3"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="6"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:11">
+      <c r="J117" s="4"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:12">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
-      <c r="G118" s="4"/>
+      <c r="G118" s="3"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="6"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:11">
+      <c r="J118" s="4"/>
+      <c r="K118" s="5"/>
+      <c r="L118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:12">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-      <c r="G119" s="4"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="6"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:11">
+      <c r="G119" s="3"/>
+      <c r="H119" s="4"/>
+      <c r="K119" s="5"/>
+      <c r="L119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:12">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-      <c r="G120" s="4"/>
-      <c r="J120" s="5"/>
-      <c r="K120" s="6"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:11">
+      <c r="G120" s="3"/>
+      <c r="H120" s="4"/>
+      <c r="K120" s="5"/>
+      <c r="L120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:12">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
-      <c r="G121" s="4"/>
-      <c r="J121" s="5"/>
-      <c r="K121" s="6"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:11">
+      <c r="G121" s="3"/>
+      <c r="H121" s="4"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:12">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
-      <c r="G122" s="4"/>
-      <c r="J122" s="5"/>
-      <c r="K122" s="6"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:11">
+      <c r="G122" s="3"/>
+      <c r="H122" s="4"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:12">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-      <c r="G123" s="4"/>
-      <c r="J123" s="5"/>
-      <c r="K123" s="6"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:11">
+      <c r="G123" s="3"/>
+      <c r="H123" s="4"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:12">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-      <c r="G124" s="4"/>
-      <c r="J124" s="5"/>
-      <c r="K124" s="6"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:11">
+      <c r="G124" s="3"/>
+      <c r="H124" s="4"/>
+      <c r="K124" s="5"/>
+      <c r="L124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:12">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
-      <c r="G125" s="4"/>
-      <c r="J125" s="5"/>
-      <c r="K125" s="6"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:11">
+      <c r="G125" s="3"/>
+      <c r="H125" s="4"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:12">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
-      <c r="G126" s="4"/>
-      <c r="J126" s="5"/>
-      <c r="K126" s="6"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:11">
+      <c r="G126" s="3"/>
+      <c r="H126" s="4"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:12">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-      <c r="G127" s="4"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="6"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:11">
+      <c r="G127" s="3"/>
+      <c r="H127" s="4"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:12">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-      <c r="G128" s="4"/>
-      <c r="J128" s="5"/>
-      <c r="K128" s="6"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:11">
+      <c r="G128" s="3"/>
+      <c r="H128" s="4"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:12">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
-      <c r="G129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="6"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:11">
+      <c r="G129" s="3"/>
+      <c r="H129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="5"/>
+      <c r="L129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:12">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
-      <c r="G130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="5"/>
-      <c r="K130" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:11">
+      <c r="G130" s="3"/>
+      <c r="H130" s="4"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="5"/>
+      <c r="L130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-      <c r="G131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="5"/>
-      <c r="K131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:11">
+      <c r="G131" s="3"/>
+      <c r="H131" s="4"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:12">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-      <c r="G132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="5"/>
-      <c r="K132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:11">
+      <c r="G132" s="3"/>
+      <c r="H132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="5"/>
+      <c r="L132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:12">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
-      <c r="G133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="6"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:11">
+      <c r="G133" s="3"/>
+      <c r="H133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="5"/>
+      <c r="L133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:12">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
-      <c r="G134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="5"/>
-      <c r="K134" s="6"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:11">
+      <c r="G134" s="3"/>
+      <c r="H134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="5"/>
+      <c r="L134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:12">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-      <c r="G135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="6"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:11">
+      <c r="G135" s="3"/>
+      <c r="H135" s="4"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="5"/>
+      <c r="L135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-      <c r="G136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="6"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:11">
+      <c r="G136" s="3"/>
+      <c r="H136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="5"/>
+      <c r="L136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
-      <c r="G137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="6"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:11">
+      <c r="G137" s="3"/>
+      <c r="H137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="5"/>
+      <c r="L137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
-      <c r="G138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="5"/>
-      <c r="K138" s="6"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:11">
+      <c r="G138" s="3"/>
+      <c r="H138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="5"/>
+      <c r="L138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-      <c r="G139" s="4"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="6"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:11">
+      <c r="G139" s="3"/>
+      <c r="H139" s="4"/>
+      <c r="K139" s="5"/>
+      <c r="L139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-      <c r="G140" s="4"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="6"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:11">
+      <c r="G140" s="3"/>
+      <c r="H140" s="4"/>
+      <c r="K140" s="5"/>
+      <c r="L140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:12">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
-      <c r="G141" s="4"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="6"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:11">
+      <c r="G141" s="3"/>
+      <c r="H141" s="4"/>
+      <c r="K141" s="5"/>
+      <c r="L141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:12">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
-      <c r="G142" s="4"/>
-      <c r="J142" s="5"/>
-      <c r="K142" s="6"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:11">
+      <c r="G142" s="3"/>
+      <c r="H142" s="4"/>
+      <c r="K142" s="5"/>
+      <c r="L142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:12">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-      <c r="G143" s="4"/>
-      <c r="J143" s="5"/>
-      <c r="K143" s="6"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:11">
+      <c r="G143" s="3"/>
+      <c r="H143" s="4"/>
+      <c r="K143" s="5"/>
+      <c r="L143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:12">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-      <c r="G144" s="4"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="6"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:11">
+      <c r="G144" s="3"/>
+      <c r="H144" s="4"/>
+      <c r="K144" s="5"/>
+      <c r="L144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:12">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
-      <c r="G145" s="4"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="6"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:11">
+      <c r="G145" s="3"/>
+      <c r="H145" s="4"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:12">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
-      <c r="G146" s="4"/>
-      <c r="J146" s="5"/>
-      <c r="K146" s="6"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:11">
+      <c r="G146" s="3"/>
+      <c r="H146" s="4"/>
+      <c r="K146" s="5"/>
+      <c r="L146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:12">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
-      <c r="G147" s="4"/>
-      <c r="J147" s="5"/>
-      <c r="K147" s="6"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:11">
+      <c r="G147" s="3"/>
+      <c r="H147" s="4"/>
+      <c r="K147" s="5"/>
+      <c r="L147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:12">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
-      <c r="G148" s="4"/>
-      <c r="J148" s="5"/>
-      <c r="K148" s="6"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:11">
+      <c r="G148" s="3"/>
+      <c r="H148" s="4"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:12">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
-      <c r="G149" s="4"/>
-      <c r="J149" s="5"/>
-      <c r="K149" s="6"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:11">
+      <c r="G149" s="3"/>
+      <c r="H149" s="4"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:12">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
-      <c r="G150" s="4"/>
-      <c r="J150" s="5"/>
-      <c r="K150" s="6"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:11">
+      <c r="G150" s="3"/>
+      <c r="H150" s="4"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:12">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
-      <c r="G151" s="4"/>
-      <c r="J151" s="5"/>
-      <c r="K151" s="6"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:11">
+      <c r="G151" s="3"/>
+      <c r="H151" s="4"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:12">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
-      <c r="G152" s="4"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="6"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:11">
+      <c r="G152" s="3"/>
+      <c r="H152" s="4"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:12">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
-      <c r="G153" s="4"/>
-      <c r="J153" s="5"/>
-      <c r="K153" s="6"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:11">
+      <c r="G153" s="3"/>
+      <c r="H153" s="4"/>
+      <c r="K153" s="5"/>
+      <c r="L153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:12">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
-      <c r="G154" s="4"/>
-      <c r="J154" s="5"/>
-      <c r="K154" s="6"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:11">
+      <c r="G154" s="3"/>
+      <c r="H154" s="4"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
-      <c r="G155" s="4"/>
-      <c r="J155" s="5"/>
-      <c r="K155" s="6"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:11">
+      <c r="G155" s="3"/>
+      <c r="H155" s="4"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:12">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
-      <c r="G156" s="4"/>
-      <c r="J156" s="5"/>
-      <c r="K156" s="6"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:11">
+      <c r="G156" s="3"/>
+      <c r="H156" s="4"/>
+      <c r="K156" s="5"/>
+      <c r="L156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:12">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
-      <c r="G157" s="4"/>
-      <c r="J157" s="5"/>
-      <c r="K157" s="6"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:11">
+      <c r="G157" s="3"/>
+      <c r="H157" s="4"/>
+      <c r="K157" s="5"/>
+      <c r="L157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:12">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
-      <c r="G158" s="4"/>
-      <c r="J158" s="5"/>
-      <c r="K158" s="6"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="4"/>
+      <c r="K158" s="5"/>
+      <c r="L158" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -32,32 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1. 白银
-2. 钻石
-3. 铂金
-4. 彩金</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>序号</t>
   </si>
@@ -96,9 +71,6 @@
     <t>#对应任务</t>
   </si>
   <si>
-    <t>品质</t>
-  </si>
-  <si>
     <t>多语言ID</t>
   </si>
   <si>
@@ -112,9 +84,6 @@
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>Quality</t>
   </si>
   <si>
     <t>MedalNameId</t>
@@ -1607,24 +1576,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.725" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.175" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="20.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24" style="1" customWidth="1"/>
-    <col min="12" max="12" width="32" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.175" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1640,2843 +1608,2557 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:13">
+      <c r="K1" s="5"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:13">
+      <c r="K2" s="5"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:13">
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:13">
+      <c r="K4" s="5"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
       <c r="A5" s="8">
         <v>1150001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
         <v>1150001</v>
       </c>
-      <c r="F5" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:13">
+      <c r="K5" s="5"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
       <c r="A6" s="3">
         <v>1150002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
         <v>1150002</v>
       </c>
-      <c r="F6" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:13">
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
       <c r="A7" s="3">
         <v>1150003</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
         <v>1150003</v>
       </c>
-      <c r="F7" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:13">
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
       <c r="A8" s="3">
         <v>1150004</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
         <v>1150004</v>
       </c>
-      <c r="F8" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:13">
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
       <c r="A9" s="3">
         <v>1150005</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
         <v>1150005</v>
       </c>
-      <c r="F9" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:13">
+      <c r="K9" s="5"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
       <c r="A10" s="3">
         <v>1150006</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
         <v>1150006</v>
       </c>
-      <c r="F10" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:13">
+      <c r="K10" s="5"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="3">
         <v>1150007</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
         <v>1150007</v>
       </c>
-      <c r="F11" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:13">
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
       <c r="A12" s="3">
         <v>1150008</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
         <v>1150008</v>
       </c>
-      <c r="F12" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:13">
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
       <c r="A13" s="3">
         <v>1150009</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
         <v>1150009</v>
       </c>
-      <c r="F13" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
+      <c r="K13" s="5"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
       <c r="A14" s="3">
         <v>1150010</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
         <v>1150010</v>
       </c>
-      <c r="F14" s="3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:13">
+      <c r="K14" s="5"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
       <c r="A15" s="3">
         <v>1150011</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
         <v>1150011</v>
       </c>
-      <c r="F15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3"/>
+      <c r="E15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:13">
+      <c r="J15" s="5"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
       <c r="A16" s="3">
         <v>1150012</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
         <v>1150012</v>
       </c>
-      <c r="F16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3"/>
+      <c r="E16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:12">
+      <c r="J16" s="5"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
       <c r="A17" s="3">
         <v>1150013</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
         <v>1150013</v>
       </c>
-      <c r="F17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3"/>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
+      <c r="J17" s="5"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="3">
         <v>1150014</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
         <v>1150014</v>
       </c>
-      <c r="F18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3"/>
+      <c r="E18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:12">
+      <c r="J18" s="5"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
       <c r="A19" s="3">
         <v>1150015</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
         <v>1150015</v>
       </c>
-      <c r="F19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3"/>
+      <c r="E19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:12">
+      <c r="J19" s="5"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
       <c r="A20" s="8">
         <v>1150016</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3">
         <v>1150016</v>
       </c>
-      <c r="F20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3"/>
+      <c r="E20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:12">
+      <c r="J20" s="5"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
       <c r="A21" s="8">
         <v>1150017</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D21" s="3">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3">
         <v>1150017</v>
       </c>
-      <c r="F21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3"/>
+      <c r="E21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
+      <c r="J21" s="5"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="3">
         <v>1150018</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" s="3">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3">
         <v>1150018</v>
       </c>
-      <c r="F22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3"/>
+      <c r="E22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:12">
+      <c r="J22" s="5"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
       <c r="A23" s="3">
         <v>1150019</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" s="3">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3">
         <v>1150019</v>
       </c>
-      <c r="F23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3"/>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:12">
+      <c r="J23" s="5"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="3">
         <v>1150020</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3">
         <v>1150020</v>
       </c>
-      <c r="F24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3"/>
+      <c r="E24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
+      <c r="J24" s="5"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
       <c r="A25" s="3">
         <v>1150021</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3">
-        <v>2</v>
-      </c>
-      <c r="E25" s="3">
         <v>1150021</v>
       </c>
-      <c r="F25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3"/>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
+      <c r="J25" s="5"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
       <c r="A26" s="3">
         <v>1150022</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3">
-        <v>2</v>
-      </c>
-      <c r="E26" s="3">
         <v>1150022</v>
       </c>
-      <c r="F26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3"/>
+      <c r="E26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
+      <c r="J26" s="5"/>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
       <c r="A27" s="8">
         <v>1150023</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="3">
-        <v>2</v>
-      </c>
-      <c r="E27" s="3">
         <v>1150023</v>
       </c>
-      <c r="F27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3"/>
+      <c r="E27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:12">
+      <c r="J27" s="5"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
       <c r="A28" s="3">
         <v>1150024</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
-      </c>
-      <c r="E28" s="3">
         <v>1150024</v>
       </c>
-      <c r="F28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3"/>
+      <c r="E28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:12">
+      <c r="J28" s="5"/>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="3">
         <v>1150025</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3">
-        <v>2</v>
-      </c>
-      <c r="E29" s="3">
         <v>1150025</v>
       </c>
-      <c r="F29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3"/>
+      <c r="E29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
+      <c r="J29" s="5"/>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
       <c r="A30" s="8">
         <v>1150026</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D30" s="3">
-        <v>2</v>
-      </c>
-      <c r="E30" s="3">
         <v>1150026</v>
       </c>
-      <c r="F30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3"/>
+      <c r="E30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
+      <c r="J30" s="5"/>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
       <c r="A31" s="8">
         <v>1150027</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3">
         <v>1150027</v>
       </c>
-      <c r="F31" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3"/>
+      <c r="E31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:12">
+      <c r="J31" s="5"/>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="8">
         <v>1150028</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D32" s="3">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
         <v>1150028</v>
       </c>
-      <c r="F32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3"/>
+      <c r="E32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:12">
+      <c r="J32" s="5"/>
+      <c r="K32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="3">
         <v>1150029</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3">
         <v>1150029</v>
       </c>
-      <c r="F33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3"/>
+      <c r="E33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:12">
+      <c r="J33" s="5"/>
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="3">
         <v>1150030</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3">
-        <v>3</v>
-      </c>
-      <c r="E34" s="3">
         <v>1150030</v>
       </c>
-      <c r="F34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3"/>
+      <c r="E34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:12">
+      <c r="J34" s="5"/>
+      <c r="K34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="3">
         <v>1150031</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3">
         <v>1150031</v>
       </c>
-      <c r="F35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3"/>
+      <c r="E35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:12">
+      <c r="J35" s="5"/>
+      <c r="K35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:11">
       <c r="A36" s="8">
         <v>1150032</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3">
-        <v>3</v>
-      </c>
-      <c r="E36" s="3">
         <v>1150032</v>
       </c>
-      <c r="F36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="E36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:12">
+      <c r="J36" s="5"/>
+      <c r="K36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:11">
       <c r="A37" s="3">
         <v>1150033</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
-        <v>3</v>
-      </c>
-      <c r="E37" s="3">
         <v>1150033</v>
       </c>
-      <c r="F37" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3"/>
+      <c r="E37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:12">
+      <c r="J37" s="5"/>
+      <c r="K37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:11">
       <c r="A38" s="3">
         <v>1150034</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3">
-        <v>3</v>
-      </c>
-      <c r="E38" s="3">
         <v>1150034</v>
       </c>
-      <c r="F38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3"/>
+      <c r="E38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:12">
+      <c r="J38" s="5"/>
+      <c r="K38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:11">
       <c r="A39" s="3">
         <v>1150035</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3">
-        <v>3</v>
-      </c>
-      <c r="E39" s="3">
         <v>1150035</v>
       </c>
-      <c r="F39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3"/>
+      <c r="E39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
+      <c r="J39" s="5"/>
+      <c r="K39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:11">
       <c r="A40" s="3">
         <v>1150036</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3">
-        <v>3</v>
-      </c>
-      <c r="E40" s="3">
         <v>1150036</v>
       </c>
-      <c r="F40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3"/>
+      <c r="E40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
+      <c r="J40" s="5"/>
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:11">
       <c r="A41" s="3">
         <v>1150037</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3">
         <v>1150037</v>
       </c>
-      <c r="F41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3"/>
+      <c r="E41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
+      <c r="J41" s="5"/>
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:11">
       <c r="A42" s="3">
         <v>1150038</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3">
         <v>1150038</v>
       </c>
-      <c r="F42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3"/>
+      <c r="E42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:12">
+      <c r="J42" s="5"/>
+      <c r="K42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:11">
       <c r="A43" s="8">
         <v>1150039</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3">
         <v>1150039</v>
       </c>
-      <c r="F43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3"/>
+      <c r="E43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:12">
+      <c r="J43" s="5"/>
+      <c r="K43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:11">
       <c r="A44" s="3">
         <v>1150040</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3">
         <v>1150040</v>
       </c>
-      <c r="F44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3"/>
+      <c r="E44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:12">
+      <c r="J44" s="5"/>
+      <c r="K44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:11">
       <c r="A45" s="3">
         <v>1150041</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3">
         <v>1150041</v>
       </c>
-      <c r="F45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3"/>
+      <c r="E45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:12">
+      <c r="J45" s="5"/>
+      <c r="K45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:11">
       <c r="A46" s="8">
         <v>1150042</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D46" s="3">
-        <v>4</v>
-      </c>
-      <c r="E46" s="3">
         <v>1150042</v>
       </c>
-      <c r="F46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3"/>
+      <c r="E46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:12">
+      <c r="J46" s="5"/>
+      <c r="K46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:11">
       <c r="A47" s="3">
         <v>1150043</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3">
         <v>1150043</v>
       </c>
-      <c r="F47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3"/>
+      <c r="E47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:12">
+      <c r="J47" s="5"/>
+      <c r="K47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:11">
       <c r="A48" s="3">
         <v>1150044</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3">
         <v>1150044</v>
       </c>
-      <c r="F48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3"/>
+      <c r="E48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:12">
+      <c r="J48" s="5"/>
+      <c r="K48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:11">
       <c r="A49" s="3">
         <v>1150045</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3">
-        <v>4</v>
-      </c>
-      <c r="E49" s="3">
         <v>1150045</v>
       </c>
-      <c r="F49" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3"/>
+      <c r="E49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:12">
+      <c r="J49" s="5"/>
+      <c r="K49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:11">
       <c r="A50" s="3">
         <v>1150046</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3">
-        <v>4</v>
-      </c>
-      <c r="E50" s="3">
         <v>1150046</v>
       </c>
-      <c r="F50" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3"/>
+      <c r="E50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:12">
+      <c r="J50" s="5"/>
+      <c r="K50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:11">
       <c r="A51" s="3">
         <v>1150047</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3">
-        <v>4</v>
-      </c>
-      <c r="E51" s="3">
         <v>1150047</v>
       </c>
-      <c r="F51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3"/>
+      <c r="E51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:12">
+      <c r="J51" s="5"/>
+      <c r="K51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:11">
       <c r="A52" s="8">
         <v>1150048</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3">
         <v>1150048</v>
       </c>
-      <c r="F52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3"/>
+      <c r="E52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:12">
+      <c r="J52" s="5"/>
+      <c r="K52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:11">
       <c r="A53" s="3">
         <v>1150049</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3">
-        <v>4</v>
-      </c>
-      <c r="E53" s="3">
         <v>1150049</v>
       </c>
-      <c r="F53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3"/>
+      <c r="E53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:12">
+      <c r="J53" s="5"/>
+      <c r="K53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:11">
       <c r="A54" s="3">
         <v>1150050</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3">
-        <v>4</v>
-      </c>
-      <c r="E54" s="3">
         <v>1150050</v>
       </c>
-      <c r="F54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3"/>
+      <c r="E54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:12">
+      <c r="J54" s="5"/>
+      <c r="K54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:11">
       <c r="A55" s="3">
         <v>1150051</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3">
-        <v>4</v>
-      </c>
-      <c r="E55" s="3">
         <v>1150051</v>
       </c>
-      <c r="F55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3"/>
+      <c r="E55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:12">
+      <c r="J55" s="5"/>
+      <c r="K55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:11">
       <c r="A56" s="3">
         <v>1150052</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3">
-        <v>4</v>
-      </c>
-      <c r="E56" s="3">
         <v>1150052</v>
       </c>
-      <c r="F56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3"/>
+      <c r="E56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:12">
+      <c r="J56" s="5"/>
+      <c r="K56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:11">
       <c r="A57" s="3">
         <v>1150053</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
         <v>1150053</v>
       </c>
-      <c r="F57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3"/>
+      <c r="E57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:12">
+      <c r="J57" s="5"/>
+      <c r="K57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:11">
       <c r="A58" s="8">
         <v>1150054</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3">
         <v>1150054</v>
       </c>
-      <c r="F58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3"/>
+      <c r="E58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="6"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:12">
+      <c r="J58" s="5"/>
+      <c r="K58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:11">
       <c r="A59" s="3">
         <v>1150055</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
         <v>1150055</v>
       </c>
-      <c r="F59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="3"/>
+      <c r="E59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:12">
+      <c r="J59" s="5"/>
+      <c r="K59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:11">
       <c r="A60" s="3">
         <v>1150056</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
-        <v>4</v>
-      </c>
-      <c r="E60" s="3">
         <v>1150056</v>
       </c>
-      <c r="F60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G60" s="3"/>
+      <c r="E60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:12">
+      <c r="J60" s="5"/>
+      <c r="K60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:11">
       <c r="A61" s="3">
         <v>1150057</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3">
-        <v>4</v>
-      </c>
-      <c r="E61" s="3">
         <v>1150057</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="6"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:12">
+      <c r="J61" s="5"/>
+      <c r="K61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:11">
       <c r="A62" s="3">
         <v>1150058</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3">
         <v>1150058</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:12">
+      <c r="J62" s="5"/>
+      <c r="K62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:11">
       <c r="A63" s="3">
         <v>1150059</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3">
-        <v>4</v>
-      </c>
-      <c r="E63" s="3">
         <v>1150059</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:12">
+      <c r="J63" s="5"/>
+      <c r="K63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:11">
       <c r="A64" s="3">
         <v>1150060</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3">
-        <v>4</v>
-      </c>
-      <c r="E64" s="3">
         <v>1150060</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G64" s="3"/>
+      <c r="E64" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:12">
+      <c r="J64" s="5"/>
+      <c r="K64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:11">
       <c r="A65" s="3">
         <v>1150061</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3">
-        <v>4</v>
-      </c>
-      <c r="E65" s="3">
         <v>1150061</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G65" s="3"/>
+      <c r="E65" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:12">
+      <c r="J65" s="5"/>
+      <c r="K65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:11">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:12">
+      <c r="J66" s="5"/>
+      <c r="K66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:11">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:12">
+      <c r="J67" s="5"/>
+      <c r="K67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:11">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:12">
+      <c r="J68" s="5"/>
+      <c r="K68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:11">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:12">
+      <c r="J69" s="5"/>
+      <c r="K69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:11">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:12">
+      <c r="J70" s="5"/>
+      <c r="K70" s="6"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:11">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:12">
+      <c r="J71" s="5"/>
+      <c r="K71" s="6"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:11">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
+      <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="6"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:12">
+      <c r="J72" s="5"/>
+      <c r="K72" s="6"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:11">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="6"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:12">
+      <c r="J73" s="5"/>
+      <c r="K73" s="6"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:11">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
+      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="6"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:12">
+      <c r="J74" s="5"/>
+      <c r="K74" s="6"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:11">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="6"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:12">
+      <c r="J75" s="5"/>
+      <c r="K75" s="6"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:11">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:12">
+      <c r="J76" s="5"/>
+      <c r="K76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:11">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
+      <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:12">
+      <c r="J77" s="5"/>
+      <c r="K77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:11">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
+      <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:12">
+      <c r="J78" s="5"/>
+      <c r="K78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
+      <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:12">
+      <c r="J79" s="5"/>
+      <c r="K79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
+      <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:12">
+      <c r="J80" s="5"/>
+      <c r="K80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:12">
+      <c r="J81" s="5"/>
+      <c r="K81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
+      <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="5"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:12">
+      <c r="J82" s="5"/>
+      <c r="K82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
+      <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:12">
+      <c r="J83" s="5"/>
+      <c r="K83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
+      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:12">
+      <c r="J84" s="5"/>
+      <c r="K84" s="6"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
+      <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:12">
+      <c r="J85" s="5"/>
+      <c r="K85" s="6"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="5"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:12">
+      <c r="J86" s="5"/>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
+      <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="5"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:12">
+      <c r="J87" s="5"/>
+      <c r="K87" s="6"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
+      <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="5"/>
-      <c r="L88" s="6"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:12">
+      <c r="J88" s="5"/>
+      <c r="K88" s="6"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:11">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="6"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:12">
+      <c r="J89" s="5"/>
+      <c r="K89" s="6"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:11">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="6"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:12">
+      <c r="J90" s="5"/>
+      <c r="K90" s="6"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="6"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:12">
+      <c r="J91" s="5"/>
+      <c r="K91" s="6"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
+      <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="6"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:12">
+      <c r="J92" s="5"/>
+      <c r="K92" s="6"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:11">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
+      <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:12">
+      <c r="J93" s="5"/>
+      <c r="K93" s="6"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:11">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+      <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="6"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:12">
+      <c r="J94" s="5"/>
+      <c r="K94" s="6"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:11">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+      <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="6"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:12">
+      <c r="J95" s="5"/>
+      <c r="K95" s="6"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:11">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+      <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="6"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:12">
+      <c r="J96" s="5"/>
+      <c r="K96" s="6"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:11">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
+      <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="6"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:12">
+      <c r="J97" s="5"/>
+      <c r="K97" s="6"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
+      <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="6"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:12">
+      <c r="J98" s="5"/>
+      <c r="K98" s="6"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:11">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
+      <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="6"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
+      <c r="J99" s="5"/>
+      <c r="K99" s="6"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:11">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:12">
+      <c r="J100" s="5"/>
+      <c r="K100" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:11">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:12">
+      <c r="J101" s="5"/>
+      <c r="K101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:11">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
+      <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:12">
+      <c r="J102" s="5"/>
+      <c r="K102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:11">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
+      <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="6"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:12">
+      <c r="J103" s="5"/>
+      <c r="K103" s="6"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:11">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
+      <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:12">
+      <c r="J104" s="5"/>
+      <c r="K104" s="6"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:11">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
+      <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:12">
+      <c r="J105" s="5"/>
+      <c r="K105" s="6"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:11">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
+      <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:12">
+      <c r="J106" s="5"/>
+      <c r="K106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:11">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
+      <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:12">
+      <c r="J107" s="5"/>
+      <c r="K107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:11">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
+      <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="5"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:12">
+      <c r="J108" s="5"/>
+      <c r="K108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:11">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
+      <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:12">
+      <c r="J109" s="5"/>
+      <c r="K109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:11">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
+      <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:12">
+      <c r="J110" s="5"/>
+      <c r="K110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:11">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
+      <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:12">
+      <c r="J111" s="5"/>
+      <c r="K111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:11">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
+      <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:12">
+      <c r="J112" s="5"/>
+      <c r="K112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:11">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
+      <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:12">
+      <c r="J113" s="5"/>
+      <c r="K113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:11">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
+      <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="6"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:12">
+      <c r="J114" s="5"/>
+      <c r="K114" s="6"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:11">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
+      <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="6"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:12">
+      <c r="J115" s="5"/>
+      <c r="K115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:11">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
+      <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="6"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:12">
+      <c r="J116" s="5"/>
+      <c r="K116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:11">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
+      <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="6"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:12">
+      <c r="J117" s="5"/>
+      <c r="K117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:11">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
+      <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="6"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:12">
+      <c r="J118" s="5"/>
+      <c r="K118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:11">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="4"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="6"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:12">
+      <c r="G119" s="4"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="4"/>
-      <c r="K120" s="5"/>
-      <c r="L120" s="6"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:12">
+      <c r="G120" s="4"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="4"/>
-      <c r="K121" s="5"/>
-      <c r="L121" s="6"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:12">
+      <c r="G121" s="4"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="4"/>
-      <c r="K122" s="5"/>
-      <c r="L122" s="6"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:12">
+      <c r="G122" s="4"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="4"/>
-      <c r="K123" s="5"/>
-      <c r="L123" s="6"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:12">
+      <c r="G123" s="4"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="4"/>
-      <c r="K124" s="5"/>
-      <c r="L124" s="6"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:12">
+      <c r="G124" s="4"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="4"/>
-      <c r="K125" s="5"/>
-      <c r="L125" s="6"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:12">
+      <c r="G125" s="4"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="4"/>
-      <c r="K126" s="5"/>
-      <c r="L126" s="6"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:12">
+      <c r="G126" s="4"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="6"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="4"/>
-      <c r="K127" s="5"/>
-      <c r="L127" s="6"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:12">
+      <c r="G127" s="4"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="4"/>
-      <c r="K128" s="5"/>
-      <c r="L128" s="6"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:12">
+      <c r="G128" s="4"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="6"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:12">
+      <c r="G129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:11">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:12">
+      <c r="G130" s="4"/>
+      <c r="I130" s="4"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:11">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:12">
+      <c r="G131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:11">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="5"/>
-      <c r="L132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:12">
+      <c r="G132" s="4"/>
+      <c r="I132" s="4"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:11">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="6"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:12">
+      <c r="G133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:11">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
-      <c r="G134" s="3"/>
-      <c r="H134" s="4"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="6"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:12">
+      <c r="G134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:11">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="6"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:12">
+      <c r="G135" s="4"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:11">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-      <c r="G136" s="3"/>
-      <c r="H136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="6"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:12">
+      <c r="G136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:11">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="6"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:12">
+      <c r="G137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:11">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="6"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:12">
+      <c r="G138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="6"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:11">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="4"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="6"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:12">
+      <c r="G139" s="4"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:11">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="4"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="6"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:12">
+      <c r="G140" s="4"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:11">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
-      <c r="G141" s="3"/>
-      <c r="H141" s="4"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="6"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:12">
+      <c r="G141" s="4"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:11">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="4"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="6"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:12">
+      <c r="G142" s="4"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:11">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="4"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="6"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:12">
+      <c r="G143" s="4"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:11">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-      <c r="G144" s="3"/>
-      <c r="H144" s="4"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="6"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:12">
+      <c r="G144" s="4"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="6"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:11">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="4"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="6"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:12">
+      <c r="G145" s="4"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:11">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="4"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="6"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:12">
+      <c r="G146" s="4"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:11">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="4"/>
-      <c r="K147" s="5"/>
-      <c r="L147" s="6"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:12">
+      <c r="G147" s="4"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:11">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="4"/>
-      <c r="K148" s="5"/>
-      <c r="L148" s="6"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:12">
+      <c r="G148" s="4"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:11">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
-      <c r="G149" s="3"/>
-      <c r="H149" s="4"/>
-      <c r="K149" s="5"/>
-      <c r="L149" s="6"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:12">
+      <c r="G149" s="4"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:11">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
-      <c r="G150" s="3"/>
-      <c r="H150" s="4"/>
-      <c r="K150" s="5"/>
-      <c r="L150" s="6"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:12">
+      <c r="G150" s="4"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="6"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:11">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
-      <c r="G151" s="3"/>
-      <c r="H151" s="4"/>
-      <c r="K151" s="5"/>
-      <c r="L151" s="6"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:12">
+      <c r="G151" s="4"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
-      <c r="G152" s="3"/>
-      <c r="H152" s="4"/>
-      <c r="K152" s="5"/>
-      <c r="L152" s="6"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:12">
+      <c r="G152" s="4"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:11">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
-      <c r="G153" s="3"/>
-      <c r="H153" s="4"/>
-      <c r="K153" s="5"/>
-      <c r="L153" s="6"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:12">
+      <c r="G153" s="4"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:11">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
-      <c r="G154" s="3"/>
-      <c r="H154" s="4"/>
-      <c r="K154" s="5"/>
-      <c r="L154" s="6"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:12">
+      <c r="G154" s="4"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
-      <c r="G155" s="3"/>
-      <c r="H155" s="4"/>
-      <c r="K155" s="5"/>
-      <c r="L155" s="6"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:12">
+      <c r="G155" s="4"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
-      <c r="G156" s="3"/>
-      <c r="H156" s="4"/>
-      <c r="K156" s="5"/>
-      <c r="L156" s="6"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:12">
+      <c r="G156" s="4"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="6"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
-      <c r="G157" s="3"/>
-      <c r="H157" s="4"/>
-      <c r="K157" s="5"/>
-      <c r="L157" s="6"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:12">
+      <c r="G157" s="4"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
-      <c r="G158" s="3"/>
-      <c r="H158" s="4"/>
-      <c r="K158" s="5"/>
-      <c r="L158" s="6"/>
+      <c r="G158" s="4"/>
+      <c r="J158" s="5"/>
+      <c r="K158" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/MedalList.xlsx
+++ b/hall/resources/sample/MedalList.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -95,79 +95,73 @@
     <t>打卡卫士</t>
   </si>
   <si>
-    <t>累积登陆N天</t>
+    <t>累积：登陆N天</t>
   </si>
   <si>
     <t>成长之路</t>
   </si>
   <si>
-    <t>角色等级达到N级</t>
+    <t>累积：等级条件</t>
   </si>
   <si>
     <t>转轮高手</t>
   </si>
   <si>
-    <t>SLOT游戏旋转N次</t>
+    <t>累积：触发SWEET WIN N次</t>
   </si>
   <si>
     <t>大赢家</t>
   </si>
   <si>
-    <t>SLOT游戏赢奖N金币</t>
+    <t>累积：触发免费游戏模式N次</t>
   </si>
   <si>
     <t>转轮精英</t>
   </si>
   <si>
-    <t>SLOT游戏获得N个X道具</t>
+    <t>累积：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
     <t>建筑大师</t>
   </si>
   <si>
-    <t>拥有N个X级以上的建筑</t>
+    <t>累积：建筑升级N次</t>
   </si>
   <si>
     <t>人气之王</t>
   </si>
   <si>
-    <t>拥有N个X星以上的游客</t>
+    <t>累积：拥有N个X星雇员</t>
   </si>
   <si>
     <t>团队高管</t>
   </si>
   <si>
-    <t>拥有N个X星以上的雇员</t>
-  </si>
-  <si>
     <t>培养能手</t>
   </si>
   <si>
-    <t>拥有N个X星娱乐类型的雇员</t>
+    <t>累积：触发MINI奖池N次</t>
   </si>
   <si>
     <t>培养大师</t>
   </si>
   <si>
-    <t>拥有N个X星休闲类型的雇员</t>
-  </si>
-  <si>
     <t>VIP专享</t>
   </si>
   <si>
-    <t>角色VIP等级达到N级</t>
+    <t>累积：观看N次广告</t>
   </si>
   <si>
     <t>研发院士</t>
   </si>
   <si>
-    <t>研究院的研发能力达到X</t>
-  </si>
-  <si>
     <t>社交精英</t>
   </si>
   <si>
     <t>精英团队</t>
+  </si>
+  <si>
+    <t>累积：研发N个游戏</t>
   </si>
   <si>
     <t>游戏大亨</t>
@@ -1517,7 +1511,9 @@
       <c r="E5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="9">
+        <v>2150001</v>
+      </c>
       <c r="G5" s="9"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
@@ -1541,7 +1537,9 @@
       <c r="E6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="9">
+        <v>2150002</v>
+      </c>
       <c r="G6" s="9"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
@@ -1565,7 +1563,9 @@
       <c r="E7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="9">
+        <v>2150003</v>
+      </c>
       <c r="G7" s="9"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
@@ -1589,7 +1589,9 @@
       <c r="E8" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="9">
+        <v>2150004</v>
+      </c>
       <c r="G8" s="9"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
@@ -1613,7 +1615,9 @@
       <c r="E9" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="9">
+        <v>2150005</v>
+      </c>
       <c r="G9" s="9"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
@@ -1637,7 +1641,9 @@
       <c r="E10" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="9">
+        <v>2150016</v>
+      </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
@@ -1660,7 +1666,9 @@
       <c r="E11" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="9">
+        <v>2150017</v>
+      </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -1675,7 +1683,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="9">
         <v>1150018</v>
@@ -1683,7 +1691,9 @@
       <c r="E12" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="9">
+        <v>2150018</v>
+      </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -1695,10 +1705,10 @@
         <v>1150019</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="D13" s="9">
         <v>1150019</v>
@@ -1706,7 +1716,9 @@
       <c r="E13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="F13" s="9">
+        <v>2150019</v>
+      </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -1718,10 +1730,10 @@
         <v>1150020</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="9">
         <v>1150020</v>
@@ -1729,7 +1741,9 @@
       <c r="E14" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="F14" s="9">
+        <v>2150020</v>
+      </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
@@ -1741,10 +1755,10 @@
         <v>1150028</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" s="9">
         <v>1150028</v>
@@ -1752,7 +1766,9 @@
       <c r="E15" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="9"/>
+      <c r="F15" s="9">
+        <v>2150028</v>
+      </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
@@ -1764,10 +1780,10 @@
         <v>1150029</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D16" s="9">
         <v>1150029</v>
@@ -1775,7 +1791,9 @@
       <c r="E16" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="9"/>
+      <c r="F16" s="9">
+        <v>2150029</v>
+      </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
@@ -1787,16 +1805,20 @@
         <v>1150030</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="D17" s="9">
         <v>1150030</v>
       </c>
       <c r="E17" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="9">
+        <v>2150030</v>
+      </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
@@ -1808,16 +1830,20 @@
         <v>1150031</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="D18" s="9">
         <v>1150031</v>
       </c>
       <c r="E18" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="9"/>
+      <c r="F18" s="9">
+        <v>2150031</v>
+      </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
@@ -1829,16 +1855,20 @@
         <v>1150032</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="D19" s="9">
         <v>1150032</v>
       </c>
       <c r="E19" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="9">
+        <v>2150032</v>
+      </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
@@ -1850,16 +1880,20 @@
         <v>1150046</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="D20" s="9">
         <v>1150046</v>
       </c>
       <c r="E20" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="9"/>
+      <c r="F20" s="9">
+        <v>2150046</v>
+      </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
@@ -1871,16 +1905,20 @@
         <v>1150048</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="D21" s="9">
         <v>1150048</v>
       </c>
       <c r="E21" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="9"/>
+      <c r="F21" s="9">
+        <v>2150048</v>
+      </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
@@ -1892,16 +1930,20 @@
         <v>1150050</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="D22" s="9">
         <v>1150050</v>
       </c>
       <c r="E22" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F22" s="9"/>
+      <c r="F22" s="9">
+        <v>2150050</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -1913,16 +1955,20 @@
         <v>1150053</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="D23" s="9">
         <v>1150053</v>
       </c>
       <c r="E23" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="9"/>
+      <c r="F23" s="9">
+        <v>2150053</v>
+      </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -1934,16 +1980,20 @@
         <v>1150054</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="D24" s="9">
         <v>1150054</v>
       </c>
       <c r="E24" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F24" s="9"/>
+      <c r="F24" s="9">
+        <v>2150054</v>
+      </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
